--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\重要AI用\和室再占領作戦\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA659B0E-F31E-493A-8F81-EFA598B80177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5268200F-B1EC-4A23-BB81-93303BD517DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\重要AI用\和室再占領作戦\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319D5D2B-27A5-45C1-9AC3-939F2D2D7513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EAB052-A85C-476F-8590-33DF8157DC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24300" yWindow="1515" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="1173">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3249,6 +3249,336 @@
   <si>
     <t>スピーカー</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインキーボード</t>
+  </si>
+  <si>
+    <t>FILCO製</t>
+  </si>
+  <si>
+    <t>有線フルキーボード（ブラック）</t>
+  </si>
+  <si>
+    <t>トラックボールマウス</t>
+  </si>
+  <si>
+    <t>ロジクール製</t>
+  </si>
+  <si>
+    <t>有線トラックボール（グレー本体、赤ボール）</t>
+  </si>
+  <si>
+    <t>サブマウス</t>
+  </si>
+  <si>
+    <t>ワイヤレス/有線マウス（レッド×ブラック）</t>
+  </si>
+  <si>
+    <t>モニター</t>
+  </si>
+  <si>
+    <t>計3台（中央：大型ワイド、左右：サブモニター）</t>
+  </si>
+  <si>
+    <t>USBハブ</t>
+  </si>
+  <si>
+    <t>スイッチ付きマルチポートUSBハブ（デスク右側）</t>
+  </si>
+  <si>
+    <t>PCステッカー</t>
+  </si>
+  <si>
+    <t>「Diginnos」ロゴステッカー（デスク右奥）</t>
+  </si>
+  <si>
+    <t>カッターマット</t>
+  </si>
+  <si>
+    <t>緑色（マス目付き、中央左寄り）</t>
+  </si>
+  <si>
+    <t>ペン立て</t>
+  </si>
+  <si>
+    <t>2箇所（ピンク×黒のチェック柄、クリアタイプ）</t>
+  </si>
+  <si>
+    <t>筆記具・工具</t>
+  </si>
+  <si>
+    <t>サクラクレパス「マイネーム」（黒・赤）、青柄のカッター、ピンセット</t>
+  </si>
+  <si>
+    <t>固形アラビックのり（ヤマト）、スティックのり（STICK</t>
+  </si>
+  <si>
+    <t>GLUE）2本</t>
+  </si>
+  <si>
+    <t>メモ・ノート類</t>
+  </si>
+  <si>
+    <t>緑色表紙のリングノート（めくり式ラベルシート付き）</t>
+  </si>
+  <si>
+    <t>付箋</t>
+  </si>
+  <si>
+    <t>プラスチックケース入り黄緑色付箋（「ひらく」の表記あり）</t>
+  </si>
+  <si>
+    <t>テープカッター</t>
+  </si>
+  <si>
+    <t>ピンク色（セロハンテープ用）</t>
+  </si>
+  <si>
+    <t>パンチ</t>
+  </si>
+  <si>
+    <t>2穴パンチ（ブラック）</t>
+  </si>
+  <si>
+    <t>マグネットトレイ</t>
+  </si>
+  <si>
+    <t>丸型金属製トレイ</t>
+  </si>
+  <si>
+    <t>プラスチックカゴ</t>
+  </si>
+  <si>
+    <t>ピンク色（大・小の計2個）</t>
+  </si>
+  <si>
+    <t>スプレー缶</t>
+  </si>
+  <si>
+    <t>フマキラー</t>
+  </si>
+  <si>
+    <t>Aダブルジェット（ピンクのカゴ内）</t>
+  </si>
+  <si>
+    <t>木製ケース</t>
+  </si>
+  <si>
+    <t>丸型・蓋付き（木目調/和風デザイン）</t>
+  </si>
+  <si>
+    <t>衛生・日用品</t>
+  </si>
+  <si>
+    <t>円筒ケース入り爪楊枝、綿棒、ロールペーパー、ウェットティッシュ</t>
+  </si>
+  <si>
+    <t>ワイヤーラック</t>
+  </si>
+  <si>
+    <t>メッシュ状収納ラック（デスク奥の上段、メジャー等収納）</t>
+  </si>
+  <si>
+    <t>予備USBケーブル数本、ACアダプター、青色結束バンド</t>
+  </si>
+  <si>
+    <t>PC周辺機器</t>
+  </si>
+  <si>
+    <t>I-00257</t>
+  </si>
+  <si>
+    <t>I-00258</t>
+  </si>
+  <si>
+    <t>I-00259</t>
+  </si>
+  <si>
+    <t>I-00260</t>
+  </si>
+  <si>
+    <t>I-00261</t>
+  </si>
+  <si>
+    <t>I-00262</t>
+  </si>
+  <si>
+    <t>事務用品</t>
+  </si>
+  <si>
+    <t>I-00263</t>
+  </si>
+  <si>
+    <t>I-00264</t>
+  </si>
+  <si>
+    <t>I-00265</t>
+  </si>
+  <si>
+    <t>I-00266</t>
+  </si>
+  <si>
+    <t>I-00267</t>
+  </si>
+  <si>
+    <t>I-00268</t>
+  </si>
+  <si>
+    <t>I-00269</t>
+  </si>
+  <si>
+    <t>I-00270</t>
+  </si>
+  <si>
+    <t>I-00271</t>
+  </si>
+  <si>
+    <t>卓上小物</t>
+  </si>
+  <si>
+    <t>I-00272</t>
+  </si>
+  <si>
+    <t>I-00273</t>
+  </si>
+  <si>
+    <t>I-00274</t>
+  </si>
+  <si>
+    <t>I-00275</t>
+  </si>
+  <si>
+    <t>I-00276</t>
+  </si>
+  <si>
+    <t>I-00277</t>
+  </si>
+  <si>
+    <t>I-00278</t>
+  </si>
+  <si>
+    <t>小さいアンビル</t>
+  </si>
+  <si>
+    <t>赤</t>
+  </si>
+  <si>
+    <t>衛生用品</t>
+  </si>
+  <si>
+    <t>I-00279</t>
+  </si>
+  <si>
+    <t>耳かき</t>
+  </si>
+  <si>
+    <t>I-00281</t>
+  </si>
+  <si>
+    <t>T-0201</t>
+  </si>
+  <si>
+    <t>T-0202</t>
+  </si>
+  <si>
+    <t>天板（中）</t>
+  </si>
+  <si>
+    <t>T-0203</t>
+  </si>
+  <si>
+    <t>一段目</t>
+  </si>
+  <si>
+    <t>T-0204</t>
+  </si>
+  <si>
+    <t>二段目</t>
+  </si>
+  <si>
+    <t>T-0205</t>
+  </si>
+  <si>
+    <t>三段目</t>
+  </si>
+  <si>
+    <t>工具・作業用品</t>
+  </si>
+  <si>
+    <t>ハンダゴテステーション</t>
+  </si>
+  <si>
+    <t>温度調節ダイヤル・ハンダホルダー・ヘルピングハンズ付きの一体型機器</t>
+  </si>
+  <si>
+    <t>I-00282</t>
+  </si>
+  <si>
+    <t>糸ハンダ</t>
+  </si>
+  <si>
+    <t>ハンダゴテステーションのホルダーにセットされているリール</t>
+  </si>
+  <si>
+    <t>I-00283</t>
+  </si>
+  <si>
+    <t>耐熱シリコン作業マット</t>
+  </si>
+  <si>
+    <t>水色（上部・右側にパーツ仕切り・ネジ溝付き、中央手前）</t>
+  </si>
+  <si>
+    <t>I-00284</t>
+  </si>
+  <si>
+    <t>ボンド</t>
+  </si>
+  <si>
+    <t>コニシ製「ボンド</t>
+  </si>
+  <si>
+    <t>プラスチック用</t>
+  </si>
+  <si>
+    <t>I-00285</t>
+  </si>
+  <si>
+    <t>ハサミ</t>
+  </si>
+  <si>
+    <t>事務用ハサミ（黒・茶系ハンドル、白スタンド内）</t>
+  </si>
+  <si>
+    <t>I-00286</t>
+  </si>
+  <si>
+    <t>ペン型精密工具</t>
+  </si>
+  <si>
+    <t>黒色のペン型工具（白スタンド内）</t>
+  </si>
+  <si>
+    <t>I-00287</t>
+  </si>
+  <si>
+    <t>小型カッター</t>
+  </si>
+  <si>
+    <t>金属製、または小型のブレード工具（白スタンド内）</t>
+  </si>
+  <si>
+    <t>ステーショナリー・事務用品</t>
+  </si>
+  <si>
+    <t>I-00288</t>
+  </si>
+  <si>
+    <t>卓上マルチスタンド</t>
+  </si>
+  <si>
+    <t>白色、4つの仕切りがあるプラスチック製小物入れ</t>
   </si>
 </sst>
 </file>
@@ -17629,33 +17959,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C288,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E288">
+      <c r="E288" t="str">
         <f>アイテム項目!$A283</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F288" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E288,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G288">
+      <c r="G288" t="str">
         <f>アイテム項目!$E283</f>
-        <v>0</v>
-      </c>
-      <c r="H288">
+        <v>I-00257</v>
+      </c>
+      <c r="H288" t="str">
         <f>アイテム項目!$F283</f>
-        <v>0</v>
-      </c>
-      <c r="I288">
+        <v>メインキーボード</v>
+      </c>
+      <c r="I288" t="str">
         <f>アイテム項目!$G283</f>
-        <v>0</v>
-      </c>
-      <c r="J288">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J288" t="str">
         <f>アイテム項目!$H283</f>
-        <v>0</v>
-      </c>
-      <c r="K288">
+        <v>B</v>
+      </c>
+      <c r="K288" t="str">
         <f>アイテム項目!$I283</f>
-        <v>0</v>
+        <v>FILCO製</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -17675,33 +18005,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C289,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E289">
+      <c r="E289" t="str">
         <f>アイテム項目!$A284</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F289" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E289,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G289">
+      <c r="G289" t="str">
         <f>アイテム項目!$E284</f>
-        <v>0</v>
-      </c>
-      <c r="H289">
+        <v>I-00258</v>
+      </c>
+      <c r="H289" t="str">
         <f>アイテム項目!$F284</f>
-        <v>0</v>
-      </c>
-      <c r="I289">
+        <v>トラックボールマウス</v>
+      </c>
+      <c r="I289" t="str">
         <f>アイテム項目!$G284</f>
-        <v>0</v>
-      </c>
-      <c r="J289">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J289" t="str">
         <f>アイテム項目!$H284</f>
-        <v>0</v>
-      </c>
-      <c r="K289">
+        <v>B</v>
+      </c>
+      <c r="K289" t="str">
         <f>アイテム項目!$I284</f>
-        <v>0</v>
+        <v>ロジクール製</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -17721,33 +18051,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C290,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E290">
+      <c r="E290" t="str">
         <f>アイテム項目!$A285</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F290" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E290,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G290">
+      <c r="G290" t="str">
         <f>アイテム項目!$E285</f>
-        <v>0</v>
-      </c>
-      <c r="H290">
+        <v>I-00259</v>
+      </c>
+      <c r="H290" t="str">
         <f>アイテム項目!$F285</f>
-        <v>0</v>
-      </c>
-      <c r="I290">
+        <v>サブマウス</v>
+      </c>
+      <c r="I290" t="str">
         <f>アイテム項目!$G285</f>
-        <v>0</v>
-      </c>
-      <c r="J290">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J290" t="str">
         <f>アイテム項目!$H285</f>
-        <v>0</v>
-      </c>
-      <c r="K290">
+        <v>B</v>
+      </c>
+      <c r="K290" t="str">
         <f>アイテム項目!$I285</f>
-        <v>0</v>
+        <v>ワイヤレス/有線マウス（レッド×ブラック）</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -17767,33 +18097,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C291,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E291">
+      <c r="E291" t="str">
         <f>アイテム項目!$A286</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F291" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E291,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G291">
+      <c r="G291" t="str">
         <f>アイテム項目!$E286</f>
-        <v>0</v>
-      </c>
-      <c r="H291">
+        <v>I-00260</v>
+      </c>
+      <c r="H291" t="str">
         <f>アイテム項目!$F286</f>
-        <v>0</v>
-      </c>
-      <c r="I291">
+        <v>モニター</v>
+      </c>
+      <c r="I291" t="str">
         <f>アイテム項目!$G286</f>
-        <v>0</v>
-      </c>
-      <c r="J291">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J291" t="str">
         <f>アイテム項目!$H286</f>
-        <v>0</v>
-      </c>
-      <c r="K291">
+        <v>B</v>
+      </c>
+      <c r="K291" t="str">
         <f>アイテム項目!$I286</f>
-        <v>0</v>
+        <v>計3台（中央：大型ワイド、左右：サブモニター）</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -17813,33 +18143,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C292,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E292">
+      <c r="E292" t="str">
         <f>アイテム項目!$A287</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F292" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E292,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G292">
+      <c r="G292" t="str">
         <f>アイテム項目!$E287</f>
-        <v>0</v>
-      </c>
-      <c r="H292">
+        <v>I-00261</v>
+      </c>
+      <c r="H292" t="str">
         <f>アイテム項目!$F287</f>
-        <v>0</v>
-      </c>
-      <c r="I292">
+        <v>USBハブ</v>
+      </c>
+      <c r="I292" t="str">
         <f>アイテム項目!$G287</f>
-        <v>0</v>
-      </c>
-      <c r="J292">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J292" t="str">
         <f>アイテム項目!$H287</f>
-        <v>0</v>
-      </c>
-      <c r="K292">
+        <v>B</v>
+      </c>
+      <c r="K292" t="str">
         <f>アイテム項目!$I287</f>
-        <v>0</v>
+        <v>スイッチ付きマルチポートUSBハブ（デスク右側）</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -17859,33 +18189,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C293,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E293">
+      <c r="E293" t="str">
         <f>アイテム項目!$A288</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F293" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E293,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G293">
+      <c r="G293" t="str">
         <f>アイテム項目!$E288</f>
-        <v>0</v>
-      </c>
-      <c r="H293">
+        <v>I-00262</v>
+      </c>
+      <c r="H293" t="str">
         <f>アイテム項目!$F288</f>
-        <v>0</v>
-      </c>
-      <c r="I293">
+        <v>PCステッカー</v>
+      </c>
+      <c r="I293" t="str">
         <f>アイテム項目!$G288</f>
-        <v>0</v>
-      </c>
-      <c r="J293">
+        <v>PC周辺機器</v>
+      </c>
+      <c r="J293" t="str">
         <f>アイテム項目!$H288</f>
-        <v>0</v>
-      </c>
-      <c r="K293">
+        <v>B</v>
+      </c>
+      <c r="K293" t="str">
         <f>アイテム項目!$I288</f>
-        <v>0</v>
+        <v>「Diginnos」ロゴステッカー（デスク右奥）</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -17905,33 +18235,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C294,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E294">
+      <c r="E294" t="str">
         <f>アイテム項目!$A289</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F294" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E294,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G294">
+      <c r="G294" t="str">
         <f>アイテム項目!$E289</f>
-        <v>0</v>
-      </c>
-      <c r="H294">
+        <v>I-00263</v>
+      </c>
+      <c r="H294" t="str">
         <f>アイテム項目!$F289</f>
-        <v>0</v>
-      </c>
-      <c r="I294">
+        <v>カッターマット</v>
+      </c>
+      <c r="I294" t="str">
         <f>アイテム項目!$G289</f>
-        <v>0</v>
-      </c>
-      <c r="J294">
+        <v>事務用品</v>
+      </c>
+      <c r="J294" t="str">
         <f>アイテム項目!$H289</f>
-        <v>0</v>
-      </c>
-      <c r="K294">
+        <v>B</v>
+      </c>
+      <c r="K294" t="str">
         <f>アイテム項目!$I289</f>
-        <v>0</v>
+        <v>緑色（マス目付き、中央左寄り）</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -17951,33 +18281,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C295,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E295">
+      <c r="E295" t="str">
         <f>アイテム項目!$A290</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F295" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E295,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G295">
+      <c r="G295" t="str">
         <f>アイテム項目!$E290</f>
-        <v>0</v>
-      </c>
-      <c r="H295">
+        <v>I-00264</v>
+      </c>
+      <c r="H295" t="str">
         <f>アイテム項目!$F290</f>
-        <v>0</v>
-      </c>
-      <c r="I295">
+        <v>ペン立て</v>
+      </c>
+      <c r="I295" t="str">
         <f>アイテム項目!$G290</f>
-        <v>0</v>
-      </c>
-      <c r="J295">
+        <v>事務用品</v>
+      </c>
+      <c r="J295" t="str">
         <f>アイテム項目!$H290</f>
-        <v>0</v>
-      </c>
-      <c r="K295">
+        <v>B</v>
+      </c>
+      <c r="K295" t="str">
         <f>アイテム項目!$I290</f>
-        <v>0</v>
+        <v>2箇所（ピンク×黒のチェック柄、クリアタイプ）</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -17997,33 +18327,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C296,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E296">
+      <c r="E296" t="str">
         <f>アイテム項目!$A291</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F296" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E296,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G296">
+      <c r="G296" t="str">
         <f>アイテム項目!$E291</f>
-        <v>0</v>
-      </c>
-      <c r="H296">
+        <v>I-00265</v>
+      </c>
+      <c r="H296" t="str">
         <f>アイテム項目!$F291</f>
-        <v>0</v>
-      </c>
-      <c r="I296">
+        <v>筆記具・工具</v>
+      </c>
+      <c r="I296" t="str">
         <f>アイテム項目!$G291</f>
-        <v>0</v>
-      </c>
-      <c r="J296">
+        <v>事務用品</v>
+      </c>
+      <c r="J296" t="str">
         <f>アイテム項目!$H291</f>
-        <v>0</v>
-      </c>
-      <c r="K296">
+        <v>B</v>
+      </c>
+      <c r="K296" t="str">
         <f>アイテム項目!$I291</f>
-        <v>0</v>
+        <v>サクラクレパス「マイネーム」（黒・赤）、青柄のカッター、ピンセット</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -18043,33 +18373,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C297,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E297">
+      <c r="E297" t="str">
         <f>アイテム項目!$A292</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F297" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E297,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G297">
+      <c r="G297" t="str">
         <f>アイテム項目!$E292</f>
-        <v>0</v>
-      </c>
-      <c r="H297">
+        <v>I-00266</v>
+      </c>
+      <c r="H297" t="str">
         <f>アイテム項目!$F292</f>
-        <v>0</v>
-      </c>
-      <c r="I297">
+        <v>接着剤</v>
+      </c>
+      <c r="I297" t="str">
         <f>アイテム項目!$G292</f>
-        <v>0</v>
-      </c>
-      <c r="J297">
+        <v>事務用品</v>
+      </c>
+      <c r="J297" t="str">
         <f>アイテム項目!$H292</f>
-        <v>0</v>
-      </c>
-      <c r="K297">
+        <v>B</v>
+      </c>
+      <c r="K297" t="str">
         <f>アイテム項目!$I292</f>
-        <v>0</v>
+        <v>固形アラビックのり（ヤマト）、スティックのり（STICK</v>
       </c>
     </row>
     <row r="298" spans="1:11">
@@ -18089,33 +18419,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C298,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E298">
+      <c r="E298" t="str">
         <f>アイテム項目!$A293</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F298" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E298,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G298">
+      <c r="G298" t="str">
         <f>アイテム項目!$E293</f>
-        <v>0</v>
-      </c>
-      <c r="H298">
+        <v>I-00267</v>
+      </c>
+      <c r="H298" t="str">
         <f>アイテム項目!$F293</f>
-        <v>0</v>
-      </c>
-      <c r="I298">
+        <v>メモ・ノート類</v>
+      </c>
+      <c r="I298" t="str">
         <f>アイテム項目!$G293</f>
-        <v>0</v>
-      </c>
-      <c r="J298">
+        <v>事務用品</v>
+      </c>
+      <c r="J298" t="str">
         <f>アイテム項目!$H293</f>
-        <v>0</v>
-      </c>
-      <c r="K298">
+        <v>B</v>
+      </c>
+      <c r="K298" t="str">
         <f>アイテム項目!$I293</f>
-        <v>0</v>
+        <v>緑色表紙のリングノート（めくり式ラベルシート付き）</v>
       </c>
     </row>
     <row r="299" spans="1:11">
@@ -18135,33 +18465,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C299,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E299">
+      <c r="E299" t="str">
         <f>アイテム項目!$A294</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F299" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E299,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G299">
+      <c r="G299" t="str">
         <f>アイテム項目!$E294</f>
-        <v>0</v>
-      </c>
-      <c r="H299">
+        <v>I-00268</v>
+      </c>
+      <c r="H299" t="str">
         <f>アイテム項目!$F294</f>
-        <v>0</v>
-      </c>
-      <c r="I299">
+        <v>付箋</v>
+      </c>
+      <c r="I299" t="str">
         <f>アイテム項目!$G294</f>
-        <v>0</v>
-      </c>
-      <c r="J299">
+        <v>事務用品</v>
+      </c>
+      <c r="J299" t="str">
         <f>アイテム項目!$H294</f>
-        <v>0</v>
-      </c>
-      <c r="K299">
+        <v>B</v>
+      </c>
+      <c r="K299" t="str">
         <f>アイテム項目!$I294</f>
-        <v>0</v>
+        <v>プラスチックケース入り黄緑色付箋（「ひらく」の表記あり）</v>
       </c>
     </row>
     <row r="300" spans="1:11">
@@ -18181,33 +18511,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C300,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E300">
+      <c r="E300" t="str">
         <f>アイテム項目!$A295</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F300" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E300,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G300">
+      <c r="G300" t="str">
         <f>アイテム項目!$E295</f>
-        <v>0</v>
-      </c>
-      <c r="H300">
+        <v>I-00269</v>
+      </c>
+      <c r="H300" t="str">
         <f>アイテム項目!$F295</f>
-        <v>0</v>
-      </c>
-      <c r="I300">
+        <v>テープカッター</v>
+      </c>
+      <c r="I300" t="str">
         <f>アイテム項目!$G295</f>
-        <v>0</v>
-      </c>
-      <c r="J300">
+        <v>事務用品</v>
+      </c>
+      <c r="J300" t="str">
         <f>アイテム項目!$H295</f>
-        <v>0</v>
-      </c>
-      <c r="K300">
+        <v>B</v>
+      </c>
+      <c r="K300" t="str">
         <f>アイテム項目!$I295</f>
-        <v>0</v>
+        <v>ピンク色（セロハンテープ用）</v>
       </c>
     </row>
     <row r="301" spans="1:11">
@@ -18227,33 +18557,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C301,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E301">
+      <c r="E301" t="str">
         <f>アイテム項目!$A296</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F301" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E301,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G301">
+      <c r="G301" t="str">
         <f>アイテム項目!$E296</f>
-        <v>0</v>
-      </c>
-      <c r="H301">
+        <v>I-00270</v>
+      </c>
+      <c r="H301" t="str">
         <f>アイテム項目!$F296</f>
-        <v>0</v>
-      </c>
-      <c r="I301">
+        <v>パンチ</v>
+      </c>
+      <c r="I301" t="str">
         <f>アイテム項目!$G296</f>
-        <v>0</v>
-      </c>
-      <c r="J301">
+        <v>事務用品</v>
+      </c>
+      <c r="J301" t="str">
         <f>アイテム項目!$H296</f>
-        <v>0</v>
-      </c>
-      <c r="K301">
+        <v>B</v>
+      </c>
+      <c r="K301" t="str">
         <f>アイテム項目!$I296</f>
-        <v>0</v>
+        <v>2穴パンチ（ブラック）</v>
       </c>
     </row>
     <row r="302" spans="1:11">
@@ -18273,33 +18603,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C302,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E302">
+      <c r="E302" t="str">
         <f>アイテム項目!$A297</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F302" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E302,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G302">
+      <c r="G302" t="str">
         <f>アイテム項目!$E297</f>
-        <v>0</v>
-      </c>
-      <c r="H302">
+        <v>I-00271</v>
+      </c>
+      <c r="H302" t="str">
         <f>アイテム項目!$F297</f>
-        <v>0</v>
-      </c>
-      <c r="I302">
+        <v>マグネットトレイ</v>
+      </c>
+      <c r="I302" t="str">
         <f>アイテム項目!$G297</f>
-        <v>0</v>
-      </c>
-      <c r="J302">
+        <v>事務用品</v>
+      </c>
+      <c r="J302" t="str">
         <f>アイテム項目!$H297</f>
-        <v>0</v>
-      </c>
-      <c r="K302">
+        <v>B</v>
+      </c>
+      <c r="K302" t="str">
         <f>アイテム項目!$I297</f>
-        <v>0</v>
+        <v>丸型金属製トレイ</v>
       </c>
     </row>
     <row r="303" spans="1:11">
@@ -18319,33 +18649,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C303,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E303">
+      <c r="E303" t="str">
         <f>アイテム項目!$A298</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F303" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E303,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G303">
+      <c r="G303" t="str">
         <f>アイテム項目!$E298</f>
-        <v>0</v>
-      </c>
-      <c r="H303">
+        <v>I-00272</v>
+      </c>
+      <c r="H303" t="str">
         <f>アイテム項目!$F298</f>
-        <v>0</v>
-      </c>
-      <c r="I303">
+        <v>プラスチックカゴ</v>
+      </c>
+      <c r="I303" t="str">
         <f>アイテム項目!$G298</f>
-        <v>0</v>
-      </c>
-      <c r="J303">
+        <v>卓上小物</v>
+      </c>
+      <c r="J303" t="str">
         <f>アイテム項目!$H298</f>
-        <v>0</v>
-      </c>
-      <c r="K303">
+        <v>B</v>
+      </c>
+      <c r="K303" t="str">
         <f>アイテム項目!$I298</f>
-        <v>0</v>
+        <v>ピンク色（大・小の計2個）</v>
       </c>
     </row>
     <row r="304" spans="1:11">
@@ -18365,33 +18695,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C304,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E304">
+      <c r="E304" t="str">
         <f>アイテム項目!$A299</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F304" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E304,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G304">
+      <c r="G304" t="str">
         <f>アイテム項目!$E299</f>
-        <v>0</v>
-      </c>
-      <c r="H304">
+        <v>I-00273</v>
+      </c>
+      <c r="H304" t="str">
         <f>アイテム項目!$F299</f>
-        <v>0</v>
-      </c>
-      <c r="I304">
+        <v>スプレー缶</v>
+      </c>
+      <c r="I304" t="str">
         <f>アイテム項目!$G299</f>
-        <v>0</v>
-      </c>
-      <c r="J304">
+        <v>卓上小物</v>
+      </c>
+      <c r="J304" t="str">
         <f>アイテム項目!$H299</f>
-        <v>0</v>
-      </c>
-      <c r="K304">
+        <v>B</v>
+      </c>
+      <c r="K304" t="str">
         <f>アイテム項目!$I299</f>
-        <v>0</v>
+        <v>フマキラー</v>
       </c>
     </row>
     <row r="305" spans="1:11">
@@ -18411,33 +18741,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C305,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E305">
+      <c r="E305" t="str">
         <f>アイテム項目!$A300</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F305" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E305,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G305">
+      <c r="G305" t="str">
         <f>アイテム項目!$E300</f>
-        <v>0</v>
-      </c>
-      <c r="H305">
+        <v>I-00274</v>
+      </c>
+      <c r="H305" t="str">
         <f>アイテム項目!$F300</f>
-        <v>0</v>
-      </c>
-      <c r="I305">
+        <v>木製ケース</v>
+      </c>
+      <c r="I305" t="str">
         <f>アイテム項目!$G300</f>
-        <v>0</v>
-      </c>
-      <c r="J305">
+        <v>卓上小物</v>
+      </c>
+      <c r="J305" t="str">
         <f>アイテム項目!$H300</f>
-        <v>0</v>
-      </c>
-      <c r="K305">
+        <v>B</v>
+      </c>
+      <c r="K305" t="str">
         <f>アイテム項目!$I300</f>
-        <v>0</v>
+        <v>丸型・蓋付き（木目調/和風デザイン）</v>
       </c>
     </row>
     <row r="306" spans="1:11">
@@ -18457,33 +18787,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C306,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E306">
+      <c r="E306" t="str">
         <f>アイテム項目!$A301</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F306" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E306,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G306">
+      <c r="G306" t="str">
         <f>アイテム項目!$E301</f>
-        <v>0</v>
-      </c>
-      <c r="H306">
+        <v>I-00275</v>
+      </c>
+      <c r="H306" t="str">
         <f>アイテム項目!$F301</f>
-        <v>0</v>
-      </c>
-      <c r="I306">
+        <v>衛生・日用品</v>
+      </c>
+      <c r="I306" t="str">
         <f>アイテム項目!$G301</f>
-        <v>0</v>
-      </c>
-      <c r="J306">
+        <v>卓上小物</v>
+      </c>
+      <c r="J306" t="str">
         <f>アイテム項目!$H301</f>
-        <v>0</v>
-      </c>
-      <c r="K306">
+        <v>B</v>
+      </c>
+      <c r="K306" t="str">
         <f>アイテム項目!$I301</f>
-        <v>0</v>
+        <v>円筒ケース入り爪楊枝、綿棒、ロールペーパー、ウェットティッシュ</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -18503,33 +18833,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C307,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E307">
+      <c r="E307" t="str">
         <f>アイテム項目!$A302</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F307" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E307,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G307">
+      <c r="G307" t="str">
         <f>アイテム項目!$E302</f>
-        <v>0</v>
-      </c>
-      <c r="H307">
+        <v>I-00276</v>
+      </c>
+      <c r="H307" t="str">
         <f>アイテム項目!$F302</f>
-        <v>0</v>
-      </c>
-      <c r="I307">
+        <v>ワイヤーラック</v>
+      </c>
+      <c r="I307" t="str">
         <f>アイテム項目!$G302</f>
-        <v>0</v>
-      </c>
-      <c r="J307">
+        <v>卓上小物</v>
+      </c>
+      <c r="J307" t="str">
         <f>アイテム項目!$H302</f>
-        <v>0</v>
-      </c>
-      <c r="K307">
+        <v>B</v>
+      </c>
+      <c r="K307" t="str">
         <f>アイテム項目!$I302</f>
-        <v>0</v>
+        <v>メッシュ状収納ラック（デスク奥の上段、メジャー等収納）</v>
       </c>
     </row>
     <row r="308" spans="1:11">
@@ -18549,33 +18879,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C308,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E308">
+      <c r="E308" t="str">
         <f>アイテム項目!$A303</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F308" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E308,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G308">
+      <c r="G308" t="str">
         <f>アイテム項目!$E303</f>
-        <v>0</v>
-      </c>
-      <c r="H308">
+        <v>I-00277</v>
+      </c>
+      <c r="H308" t="str">
         <f>アイテム項目!$F303</f>
-        <v>0</v>
-      </c>
-      <c r="I308">
+        <v>ケーブル類</v>
+      </c>
+      <c r="I308" t="str">
         <f>アイテム項目!$G303</f>
-        <v>0</v>
-      </c>
-      <c r="J308">
+        <v>卓上小物</v>
+      </c>
+      <c r="J308" t="str">
         <f>アイテム項目!$H303</f>
-        <v>0</v>
-      </c>
-      <c r="K308">
+        <v>B</v>
+      </c>
+      <c r="K308" t="str">
         <f>アイテム項目!$I303</f>
-        <v>0</v>
+        <v>予備USBケーブル数本、ACアダプター、青色結束バンド</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -18595,33 +18925,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C309,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E309">
+      <c r="E309" t="str">
         <f>アイテム項目!$A304</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F309" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E309,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G309">
+      <c r="G309" t="str">
         <f>アイテム項目!$E304</f>
-        <v>0</v>
-      </c>
-      <c r="H309">
+        <v>I-00278</v>
+      </c>
+      <c r="H309" t="str">
         <f>アイテム項目!$F304</f>
-        <v>0</v>
-      </c>
-      <c r="I309">
+        <v>小さいアンビル</v>
+      </c>
+      <c r="I309" t="str">
         <f>アイテム項目!$G304</f>
-        <v>0</v>
-      </c>
-      <c r="J309">
+        <v>工具</v>
+      </c>
+      <c r="J309" t="str">
         <f>アイテム項目!$H304</f>
-        <v>0</v>
-      </c>
-      <c r="K309">
+        <v>B</v>
+      </c>
+      <c r="K309" t="str">
         <f>アイテム項目!$I304</f>
-        <v>0</v>
+        <v>赤</v>
       </c>
     </row>
     <row r="310" spans="1:11">
@@ -18641,29 +18971,29 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C310,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E310">
+      <c r="E310" t="str">
         <f>アイテム項目!$A305</f>
-        <v>0</v>
+        <v>T-0701</v>
       </c>
       <c r="F310" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E310,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G310">
+      <c r="G310" t="str">
         <f>アイテム項目!$E305</f>
-        <v>0</v>
-      </c>
-      <c r="H310">
+        <v>I-00279</v>
+      </c>
+      <c r="H310" t="str">
         <f>アイテム項目!$F305</f>
-        <v>0</v>
-      </c>
-      <c r="I310">
+        <v>耳かき</v>
+      </c>
+      <c r="I310" t="str">
         <f>アイテム項目!$G305</f>
-        <v>0</v>
-      </c>
-      <c r="J310">
+        <v>衛生用品</v>
+      </c>
+      <c r="J310" t="str">
         <f>アイテム項目!$H305</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K310">
         <f>アイテム項目!$I305</f>
@@ -18733,33 +19063,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C312,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E312">
+      <c r="E312" t="str">
         <f>アイテム項目!$A307</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F312" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E312,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G312">
+      <c r="G312" t="str">
         <f>アイテム項目!$E307</f>
-        <v>0</v>
-      </c>
-      <c r="H312">
+        <v>I-00281</v>
+      </c>
+      <c r="H312" t="str">
         <f>アイテム項目!$F307</f>
-        <v>0</v>
-      </c>
-      <c r="I312">
-        <f>アイテム項目!$G307</f>
-        <v>0</v>
+        <v>ハンダゴテステーション</v>
+      </c>
+      <c r="I312" t="str">
+        <f>アイテム項目!$I307</f>
+        <v>温度調節ダイヤル・ハンダホルダー・ヘルピングハンズ付きの一体型機器</v>
       </c>
       <c r="J312">
         <f>アイテム項目!$H307</f>
         <v>0</v>
       </c>
-      <c r="K312">
-        <f>アイテム項目!$I307</f>
-        <v>0</v>
+      <c r="K312" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -18779,33 +19109,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C313,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E313">
+      <c r="E313" t="str">
         <f>アイテム項目!$A308</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F313" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E313,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G313">
+      <c r="G313" t="str">
         <f>アイテム項目!$E308</f>
-        <v>0</v>
-      </c>
-      <c r="H313">
+        <v>I-00282</v>
+      </c>
+      <c r="H313" t="str">
         <f>アイテム項目!$F308</f>
-        <v>0</v>
-      </c>
-      <c r="I313">
-        <f>アイテム項目!$G308</f>
-        <v>0</v>
+        <v>糸ハンダ</v>
+      </c>
+      <c r="I313" t="str">
+        <f>アイテム項目!$I308</f>
+        <v>ハンダゴテステーションのホルダーにセットされているリール</v>
       </c>
       <c r="J313">
         <f>アイテム項目!$H308</f>
         <v>0</v>
       </c>
-      <c r="K313">
-        <f>アイテム項目!$I308</f>
-        <v>0</v>
+      <c r="K313" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -18825,33 +19155,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C314,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E314">
+      <c r="E314" t="str">
         <f>アイテム項目!$A309</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F314" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E314,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G314">
+      <c r="G314" t="str">
         <f>アイテム項目!$E309</f>
-        <v>0</v>
-      </c>
-      <c r="H314">
+        <v>I-00283</v>
+      </c>
+      <c r="H314" t="str">
         <f>アイテム項目!$F309</f>
-        <v>0</v>
-      </c>
-      <c r="I314">
-        <f>アイテム項目!$G309</f>
-        <v>0</v>
+        <v>耐熱シリコン作業マット</v>
+      </c>
+      <c r="I314" t="str">
+        <f>アイテム項目!$I309</f>
+        <v>水色（上部・右側にパーツ仕切り・ネジ溝付き、中央手前）</v>
       </c>
       <c r="J314">
         <f>アイテム項目!$H309</f>
         <v>0</v>
       </c>
-      <c r="K314">
-        <f>アイテム項目!$I309</f>
-        <v>0</v>
+      <c r="K314" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -18871,33 +19201,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C315,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E315">
+      <c r="E315" t="str">
         <f>アイテム項目!$A310</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F315" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E315,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G315">
+      <c r="G315" t="str">
         <f>アイテム項目!$E310</f>
-        <v>0</v>
-      </c>
-      <c r="H315">
+        <v>I-00284</v>
+      </c>
+      <c r="H315" t="str">
         <f>アイテム項目!$F310</f>
-        <v>0</v>
-      </c>
-      <c r="I315">
-        <f>アイテム項目!$G310</f>
-        <v>0</v>
-      </c>
-      <c r="J315">
-        <f>アイテム項目!$H310</f>
-        <v>0</v>
-      </c>
-      <c r="K315">
+        <v>ボンド</v>
+      </c>
+      <c r="I315" t="str">
         <f>アイテム項目!$I310</f>
-        <v>0</v>
+        <v>コニシ製「ボンド</v>
+      </c>
+      <c r="J315" t="str">
+        <f>アイテム項目!$K310</f>
+        <v>プラスチック用</v>
+      </c>
+      <c r="K315" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="316" spans="1:11">
@@ -18917,33 +19247,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C316,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E316">
+      <c r="E316" t="str">
         <f>アイテム項目!$A311</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F316" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E316,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G316">
+      <c r="G316" t="str">
         <f>アイテム項目!$E311</f>
-        <v>0</v>
-      </c>
-      <c r="H316">
+        <v>I-00285</v>
+      </c>
+      <c r="H316" t="str">
         <f>アイテム項目!$F311</f>
-        <v>0</v>
-      </c>
-      <c r="I316">
-        <f>アイテム項目!$G311</f>
-        <v>0</v>
+        <v>ハサミ</v>
+      </c>
+      <c r="I316" t="str">
+        <f>アイテム項目!$I311</f>
+        <v>事務用ハサミ（黒・茶系ハンドル、白スタンド内）</v>
       </c>
       <c r="J316">
         <f>アイテム項目!$H311</f>
         <v>0</v>
       </c>
-      <c r="K316">
-        <f>アイテム項目!$I311</f>
-        <v>0</v>
+      <c r="K316" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="317" spans="1:11">
@@ -18963,33 +19293,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C317,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E317">
+      <c r="E317" t="str">
         <f>アイテム項目!$A312</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F317" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E317,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G317">
+      <c r="G317" t="str">
         <f>アイテム項目!$E312</f>
-        <v>0</v>
-      </c>
-      <c r="H317">
+        <v>I-00286</v>
+      </c>
+      <c r="H317" t="str">
         <f>アイテム項目!$F312</f>
-        <v>0</v>
-      </c>
-      <c r="I317">
-        <f>アイテム項目!$G312</f>
-        <v>0</v>
+        <v>ペン型精密工具</v>
+      </c>
+      <c r="I317" t="str">
+        <f>アイテム項目!$I312</f>
+        <v>黒色のペン型工具（白スタンド内）</v>
       </c>
       <c r="J317">
         <f>アイテム項目!$H312</f>
         <v>0</v>
       </c>
-      <c r="K317">
-        <f>アイテム項目!$I312</f>
-        <v>0</v>
+      <c r="K317" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="318" spans="1:11">
@@ -19009,33 +19339,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C318,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E318">
+      <c r="E318" t="str">
         <f>アイテム項目!$A313</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F318" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E318,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G318">
+      <c r="G318" t="str">
         <f>アイテム項目!$E313</f>
-        <v>0</v>
-      </c>
-      <c r="H318">
+        <v>I-00287</v>
+      </c>
+      <c r="H318" t="str">
         <f>アイテム項目!$F313</f>
-        <v>0</v>
-      </c>
-      <c r="I318">
-        <f>アイテム項目!$G313</f>
-        <v>0</v>
+        <v>小型カッター</v>
+      </c>
+      <c r="I318" t="str">
+        <f>アイテム項目!$I313</f>
+        <v>金属製、または小型のブレード工具（白スタンド内）</v>
       </c>
       <c r="J318">
         <f>アイテム項目!$H313</f>
         <v>0</v>
       </c>
-      <c r="K318">
-        <f>アイテム項目!$I313</f>
-        <v>0</v>
+      <c r="K318" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -19055,33 +19385,33 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C319,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E319">
+      <c r="E319" t="str">
         <f>アイテム項目!$A314</f>
-        <v>0</v>
+        <v>T-0201</v>
       </c>
       <c r="F319" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E319,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G319">
+      <c r="G319" t="str">
         <f>アイテム項目!$E314</f>
-        <v>0</v>
-      </c>
-      <c r="H319">
+        <v>I-00288</v>
+      </c>
+      <c r="H319" t="str">
         <f>アイテム項目!$F314</f>
-        <v>0</v>
-      </c>
-      <c r="I319">
-        <f>アイテム項目!$G314</f>
-        <v>0</v>
+        <v>卓上マルチスタンド</v>
+      </c>
+      <c r="I319" t="str">
+        <f>アイテム項目!$I314</f>
+        <v>白色、4つの仕切りがあるプラスチック製小物入れ</v>
       </c>
       <c r="J319">
         <f>アイテム項目!$H314</f>
         <v>0</v>
       </c>
-      <c r="K319">
-        <f>アイテム項目!$I314</f>
-        <v>0</v>
+      <c r="K319" t="e">
+        <f>アイテム項目!#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -53615,7 +53945,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="13.125" style="29" customWidth="1"/>
@@ -53832,53 +54162,100 @@
         <v>252</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>203</v>
+      </c>
+    </row>
     <row r="13" spans="1:8">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="H13"/>
+      <c r="A13" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="D14"/>
-      <c r="E14"/>
+      <c r="A14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1142</v>
+      </c>
       <c r="H14"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="D15"/>
-      <c r="E15"/>
+      <c r="A15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1144</v>
+      </c>
       <c r="H15"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="D16"/>
-      <c r="E16"/>
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1146</v>
+      </c>
       <c r="H16"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>253</v>
-      </c>
-      <c r="E17" t="s">
-        <v>203</v>
-      </c>
-      <c r="H17" t="s">
-        <v>254</v>
-      </c>
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="H17"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
@@ -53891,13 +54268,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E18" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="H18" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -53911,13 +54288,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E19" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -53931,13 +54308,13 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -53951,13 +54328,13 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -53968,36 +54345,36 @@
         <v>172</v>
       </c>
       <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" t="s">
+        <v>265</v>
+      </c>
+      <c r="H22" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" t="s">
         <v>267</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>268</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>269</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H23" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="29" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -54011,13 +54388,13 @@
         <v>635</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -54031,30 +54408,33 @@
         <v>635</v>
       </c>
       <c r="D31" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="29" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D32" s="29" t="s">
         <v>1060</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E32" s="29" t="s">
         <v>1052</v>
       </c>
-      <c r="H31" s="29" t="s">
+      <c r="H32" s="29" t="s">
         <v>1053</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="29" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -54068,9 +54448,26 @@
         <v>635</v>
       </c>
       <c r="D36" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="29" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D37" s="29" t="s">
         <v>1056</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E37" s="29" t="s">
         <v>1052</v>
       </c>
     </row>
@@ -54085,6 +54482,8 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
     <col min="4" max="4" width="18.625" style="29" customWidth="1"/>
     <col min="5" max="5" width="29.5" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.625" style="29" bestFit="1" customWidth="1"/>
@@ -54680,13 +55079,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:L277"/>
+  <dimension ref="A1:L314"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.75" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="7.5" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="29" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="29" customWidth="1"/>
@@ -60516,9 +60917,6 @@
         <v>830</v>
       </c>
     </row>
-    <row r="227" spans="7:7">
-      <c r="G227" s="18"/>
-    </row>
     <row r="253" spans="1:9">
       <c r="G253" s="18"/>
     </row>
@@ -61073,7 +61471,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>328</v>
       </c>
@@ -61102,7 +61500,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>328</v>
       </c>
@@ -61131,7 +61529,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>328</v>
       </c>
@@ -61160,7 +61558,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>328</v>
       </c>
@@ -61189,7 +61587,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>328</v>
       </c>
@@ -61216,6 +61614,869 @@
       </c>
       <c r="I277" t="s">
         <v>868</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="A283" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B283" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C283" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F283" s="29" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H283" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I283" s="29" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J283" s="29" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="A284" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B284" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C284" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F284" s="29" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H284" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I284" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J284" s="29" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B285" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C285" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E285" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F285" s="29" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H285" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I285" s="29" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B286" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C286" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F286" s="29" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G286" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H286" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I286" s="29" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="A287" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B287" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C287" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F287" s="29" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H287" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I287" s="29" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="A288" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B288" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C288" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E288" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F288" s="29" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H288" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I288" s="29" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B289" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C289" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F289" s="29" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H289" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I289" s="29" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B290" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C290" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F290" s="29" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G290" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H290" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I290" s="29" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B291" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C291" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E291" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F291" s="29" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H291" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I291" s="29" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B292" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C292" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F292" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H292" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I292" s="29" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J292" s="29" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B293" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C293" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F293" s="29" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H293" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I293" s="29" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B294" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C294" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F294" s="29" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G294" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H294" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I294" s="29" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="A295" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B295" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C295" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F295" s="29" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H295" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I295" s="29" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="A296" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B296" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C296" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E296" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F296" s="29" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H296" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I296" s="29" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="A297" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B297" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C297" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E297" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F297" s="29" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H297" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I297" s="29" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="A298" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B298" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C298" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F298" s="29" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H298" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I298" s="29" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="A299" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B299" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C299" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F299" s="29" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H299" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I299" s="29" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J299" s="29" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="A300" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B300" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C300" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E300" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F300" s="29" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G300" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H300" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I300" s="29" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="A301" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B301" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C301" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E301" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F301" s="29" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G301" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H301" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I301" s="29" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="A302" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B302" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C302" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E302" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F302" s="29" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G302" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H302" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I302" s="29" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="A303" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B303" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C303" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E303" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F303" s="29" t="s">
+        <v>393</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H303" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I303" s="29" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="A304" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B304" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C304" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D304" t="s">
+        <v>154</v>
+      </c>
+      <c r="E304" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F304" s="29" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G304" t="s">
+        <v>154</v>
+      </c>
+      <c r="H304" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I304" s="29" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B305" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C305" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F305" s="29" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G305" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H305" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11">
+      <c r="A307" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B307" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C307" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E307" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F307" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I307" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11">
+      <c r="A308" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B308" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C308" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E308" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F308" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I308" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11">
+      <c r="A309" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B309" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C309" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F309" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I309" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11">
+      <c r="A310" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B310" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C310" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F310" s="29" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I310" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K310" s="29" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11">
+      <c r="A311" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B311" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C311" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F311" s="29" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I311" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11">
+      <c r="A312" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B312" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C312" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E312" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F312" s="29" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I312" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11">
+      <c r="A313" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B313" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C313" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E313" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F313" s="29" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I313" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11">
+      <c r="A314" s="29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B314" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C314" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E314" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F314" s="29" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I314" t="s">
+        <v>1172</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\重要AI用\和室再占領作戦\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EAB052-A85C-476F-8590-33DF8157DC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CD9E67-25A5-421C-882E-D8A8681F75C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24300" yWindow="1515" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3226" uniqueCount="1174">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3579,6 +3579,10 @@
   </si>
   <si>
     <t>白色、4つの仕切りがあるプラスチック製小物入れ</t>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -19431,9 +19435,9 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C320,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E320">
+      <c r="E320" t="str">
         <f>アイテム項目!$A315</f>
-        <v>0</v>
+        <v>test</v>
       </c>
       <c r="F320" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E320,C項目!$D:$D,0)),"")</f>
@@ -55079,7 +55083,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:L314"/>
+  <dimension ref="A1:L315"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
@@ -62477,6 +62481,11 @@
       </c>
       <c r="I314" t="s">
         <v>1172</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11">
+      <c r="A315" s="29" t="s">
+        <v>1173</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CD9E67-25A5-421C-882E-D8A8681F75C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFF0502-13FB-49DC-96B1-51B43E02CBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24300" yWindow="1515" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24885" yWindow="3000" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3226" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="1175">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3582,6 +3582,10 @@
   </si>
   <si>
     <t>test</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>t</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -62487,6 +62491,9 @@
       <c r="A315" s="29" t="s">
         <v>1173</v>
       </c>
+      <c r="B315" s="29" t="s">
+        <v>1174</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFF0502-13FB-49DC-96B1-51B43E02CBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF852BEE-761D-48FD-93CA-34F5A6722D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24885" yWindow="3000" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3585,7 +3585,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>t</t>
+    <t>tt</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF852BEE-761D-48FD-93CA-34F5A6722D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B2E7DE-1566-408D-B8FA-BD48ADE3B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24885" yWindow="3000" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B2E7DE-1566-408D-B8FA-BD48ADE3B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC90B1DC-3A6F-48D4-9529-6C2A5FD17A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24885" yWindow="3000" windowWidth="19590" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22320" yWindow="2595" windowWidth="16155" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="1173">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3579,14 +3579,6 @@
   </si>
   <si>
     <t>白色、4つの仕切りがあるプラスチック製小物入れ</t>
-  </si>
-  <si>
-    <t>test</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>tt</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -19439,9 +19431,9 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C320,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E320" t="str">
+      <c r="E320">
         <f>アイテム項目!$A315</f>
-        <v>test</v>
+        <v>0</v>
       </c>
       <c r="F320" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E320,C項目!$D:$D,0)),"")</f>
@@ -55087,15 +55079,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:L315"/>
+  <dimension ref="A1:L314"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.75" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="23.625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="7.5" customWidth="1"/>
     <col min="8" max="8" width="7.5" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="29" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="29" customWidth="1"/>
@@ -62485,14 +62477,6 @@
       </c>
       <c r="I314" t="s">
         <v>1172</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11">
-      <c r="A315" s="29" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B315" s="29" t="s">
-        <v>1174</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC90B1DC-3A6F-48D4-9529-6C2A5FD17A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AF0D2C-7329-475B-A223-73C8C5C3798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22320" yWindow="2595" windowWidth="16155" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="1860" windowWidth="16155" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3537" uniqueCount="1276">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3579,6 +3579,315 @@
   </si>
   <si>
     <t>白色、4つの仕切りがあるプラスチック製小物入れ</t>
+  </si>
+  <si>
+    <t>I-00289</t>
+  </si>
+  <si>
+    <t>Haier リモコン</t>
+  </si>
+  <si>
+    <t>I-00290</t>
+  </si>
+  <si>
+    <t>YAMAZEN リモコン</t>
+  </si>
+  <si>
+    <t>I-00291</t>
+  </si>
+  <si>
+    <t>ミニカッター 2本入</t>
+  </si>
+  <si>
+    <t>I-00292</t>
+  </si>
+  <si>
+    <t>LED電球</t>
+  </si>
+  <si>
+    <t>I-00293</t>
+  </si>
+  <si>
+    <t>マスキングテープ</t>
+  </si>
+  <si>
+    <t>I-00294</t>
+  </si>
+  <si>
+    <t>黒 マジックペン</t>
+  </si>
+  <si>
+    <t>I-00295</t>
+  </si>
+  <si>
+    <t>TWIN MARKER 黒</t>
+  </si>
+  <si>
+    <t>I-00296</t>
+  </si>
+  <si>
+    <t>白色 歯ブラシ</t>
+  </si>
+  <si>
+    <t>I-00297</t>
+  </si>
+  <si>
+    <t>カッターナイフ</t>
+  </si>
+  <si>
+    <t>I-00298</t>
+  </si>
+  <si>
+    <t>黒 ボールペン</t>
+  </si>
+  <si>
+    <t>I-00299</t>
+  </si>
+  <si>
+    <t>グレー ペン</t>
+  </si>
+  <si>
+    <t>I-00300</t>
+  </si>
+  <si>
+    <t>白 ハサミ</t>
+  </si>
+  <si>
+    <t>I-00301</t>
+  </si>
+  <si>
+    <t>緑 指サック 5個入</t>
+  </si>
+  <si>
+    <t>I-00302</t>
+  </si>
+  <si>
+    <t>ホッチキス</t>
+  </si>
+  <si>
+    <t>I-00303</t>
+  </si>
+  <si>
+    <t>黒 テープ</t>
+  </si>
+  <si>
+    <t>I-00304</t>
+  </si>
+  <si>
+    <t>超強力両面テープ</t>
+  </si>
+  <si>
+    <t>I-00305</t>
+  </si>
+  <si>
+    <t>30cm 定規</t>
+  </si>
+  <si>
+    <t>I-00306</t>
+  </si>
+  <si>
+    <t>クリップ</t>
+  </si>
+  <si>
+    <t>I-00307</t>
+  </si>
+  <si>
+    <t>ステレオイヤホン リール式</t>
+  </si>
+  <si>
+    <t>I-00308</t>
+  </si>
+  <si>
+    <t>QianLi ツール袋</t>
+  </si>
+  <si>
+    <t>I-00309</t>
+  </si>
+  <si>
+    <t>サングラス</t>
+  </si>
+  <si>
+    <t>I-00310</t>
+  </si>
+  <si>
+    <t>リール付ストラップ</t>
+  </si>
+  <si>
+    <t>I-00311</t>
+  </si>
+  <si>
+    <t>maxell 単3乾電池</t>
+  </si>
+  <si>
+    <t>I-00312</t>
+  </si>
+  <si>
+    <t>QianLi iToor PLUS</t>
+  </si>
+  <si>
+    <t>I-00313</t>
+  </si>
+  <si>
+    <t>ボタン電池</t>
+  </si>
+  <si>
+    <t>I-00314</t>
+  </si>
+  <si>
+    <t>CPUチップ</t>
+  </si>
+  <si>
+    <t>I-00315</t>
+  </si>
+  <si>
+    <t>白いロープ</t>
+  </si>
+  <si>
+    <t>I-00316</t>
+  </si>
+  <si>
+    <t>バーコード付き袋</t>
+  </si>
+  <si>
+    <t>I-00317</t>
+  </si>
+  <si>
+    <t>目薬</t>
+  </si>
+  <si>
+    <t>I-00318</t>
+  </si>
+  <si>
+    <t>USB基板部品</t>
+  </si>
+  <si>
+    <t>I-00319</t>
+  </si>
+  <si>
+    <t>電子工作パーツ</t>
+  </si>
+  <si>
+    <t>I-00320</t>
+  </si>
+  <si>
+    <t>精密スプリング</t>
+  </si>
+  <si>
+    <t>I-00321</t>
+  </si>
+  <si>
+    <t>クリーニングブラシ</t>
+  </si>
+  <si>
+    <t>I-00322</t>
+  </si>
+  <si>
+    <t>ピンセット</t>
+  </si>
+  <si>
+    <t>I-00323</t>
+  </si>
+  <si>
+    <t>I-00324</t>
+  </si>
+  <si>
+    <t>ライター</t>
+  </si>
+  <si>
+    <t>I-00325</t>
+  </si>
+  <si>
+    <t>ウェットシート 備品</t>
+  </si>
+  <si>
+    <t>I-00326</t>
+  </si>
+  <si>
+    <t>ウェットシート Jet</t>
+  </si>
+  <si>
+    <t>I-00327</t>
+  </si>
+  <si>
+    <t>ウェットシート モニター</t>
+  </si>
+  <si>
+    <t>I-00328</t>
+  </si>
+  <si>
+    <t>ウェットシート 手前</t>
+  </si>
+  <si>
+    <t>I-00329</t>
+  </si>
+  <si>
+    <t>WATER BASED MARKER</t>
+  </si>
+  <si>
+    <t>I-00330</t>
+  </si>
+  <si>
+    <t>ピンク ハサミ</t>
+  </si>
+  <si>
+    <t>I-00331</t>
+  </si>
+  <si>
+    <t>ZEBRA 3色ボールペン</t>
+  </si>
+  <si>
+    <t>I-00332</t>
+  </si>
+  <si>
+    <t>ENERGEL ア souvenir</t>
+  </si>
+  <si>
+    <t>I-00333</t>
+  </si>
+  <si>
+    <t>PILOT 消しゴム</t>
+  </si>
+  <si>
+    <t>I-00334</t>
+  </si>
+  <si>
+    <t>青 ボールペン</t>
+  </si>
+  <si>
+    <t>I-00335</t>
+  </si>
+  <si>
+    <t>白 ボールペン</t>
+  </si>
+  <si>
+    <t>I-00336</t>
+  </si>
+  <si>
+    <t>黄色 マーカーペン</t>
+  </si>
+  <si>
+    <t>I-00337</t>
+  </si>
+  <si>
+    <t>赤 マーカーペン</t>
+  </si>
+  <si>
+    <t>I-00338</t>
+  </si>
+  <si>
+    <t>黒 シャープペン</t>
+  </si>
+  <si>
+    <t>I-00339</t>
+  </si>
+  <si>
+    <t>ビニール袋入りアイテム</t>
+  </si>
+  <si>
+    <t>I-00340</t>
+  </si>
+  <si>
+    <t>カラフル インデックス</t>
   </si>
 </sst>
 </file>
@@ -19431,21 +19740,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C320,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E320">
+      <c r="E320" t="str">
         <f>アイテム項目!$A315</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F320" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E320,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G320">
+      <c r="G320" t="str">
         <f>アイテム項目!$E315</f>
-        <v>0</v>
-      </c>
-      <c r="H320">
+        <v>I-00289</v>
+      </c>
+      <c r="H320" t="str">
         <f>アイテム項目!$F315</f>
-        <v>0</v>
+        <v>Haier リモコン</v>
       </c>
       <c r="I320">
         <f>アイテム項目!$G315</f>
@@ -19477,21 +19786,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C321,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E321">
+      <c r="E321" t="str">
         <f>アイテム項目!$A316</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F321" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E321,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G321">
+      <c r="G321" t="str">
         <f>アイテム項目!$E316</f>
-        <v>0</v>
-      </c>
-      <c r="H321">
+        <v>I-00290</v>
+      </c>
+      <c r="H321" t="str">
         <f>アイテム項目!$F316</f>
-        <v>0</v>
+        <v>YAMAZEN リモコン</v>
       </c>
       <c r="I321">
         <f>アイテム項目!$G316</f>
@@ -19523,21 +19832,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C322,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E322">
+      <c r="E322" t="str">
         <f>アイテム項目!$A317</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F322" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E322,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G322">
+      <c r="G322" t="str">
         <f>アイテム項目!$E317</f>
-        <v>0</v>
-      </c>
-      <c r="H322">
+        <v>I-00291</v>
+      </c>
+      <c r="H322" t="str">
         <f>アイテム項目!$F317</f>
-        <v>0</v>
+        <v>ミニカッター 2本入</v>
       </c>
       <c r="I322">
         <f>アイテム項目!$G317</f>
@@ -19569,21 +19878,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C323,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E323">
+      <c r="E323" t="str">
         <f>アイテム項目!$A318</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F323" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E323,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G323">
+      <c r="G323" t="str">
         <f>アイテム項目!$E318</f>
-        <v>0</v>
-      </c>
-      <c r="H323">
+        <v>I-00292</v>
+      </c>
+      <c r="H323" t="str">
         <f>アイテム項目!$F318</f>
-        <v>0</v>
+        <v>LED電球</v>
       </c>
       <c r="I323">
         <f>アイテム項目!$G318</f>
@@ -19615,21 +19924,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C324,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E324">
+      <c r="E324" t="str">
         <f>アイテム項目!$A319</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F324" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E324,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G324">
+      <c r="G324" t="str">
         <f>アイテム項目!$E319</f>
-        <v>0</v>
-      </c>
-      <c r="H324">
+        <v>I-00293</v>
+      </c>
+      <c r="H324" t="str">
         <f>アイテム項目!$F319</f>
-        <v>0</v>
+        <v>マスキングテープ</v>
       </c>
       <c r="I324">
         <f>アイテム項目!$G319</f>
@@ -19661,21 +19970,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C325,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E325">
+      <c r="E325" t="str">
         <f>アイテム項目!$A320</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F325" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E325,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G325">
+      <c r="G325" t="str">
         <f>アイテム項目!$E320</f>
-        <v>0</v>
-      </c>
-      <c r="H325">
+        <v>I-00294</v>
+      </c>
+      <c r="H325" t="str">
         <f>アイテム項目!$F320</f>
-        <v>0</v>
+        <v>黒 マジックペン</v>
       </c>
       <c r="I325">
         <f>アイテム項目!$G320</f>
@@ -19707,21 +20016,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C326,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E326">
+      <c r="E326" t="str">
         <f>アイテム項目!$A321</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F326" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E326,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G326">
+      <c r="G326" t="str">
         <f>アイテム項目!$E321</f>
-        <v>0</v>
-      </c>
-      <c r="H326">
+        <v>I-00295</v>
+      </c>
+      <c r="H326" t="str">
         <f>アイテム項目!$F321</f>
-        <v>0</v>
+        <v>TWIN MARKER 黒</v>
       </c>
       <c r="I326">
         <f>アイテム項目!$G321</f>
@@ -19753,21 +20062,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C327,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E327">
+      <c r="E327" t="str">
         <f>アイテム項目!$A322</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F327" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E327,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G327">
+      <c r="G327" t="str">
         <f>アイテム項目!$E322</f>
-        <v>0</v>
-      </c>
-      <c r="H327">
+        <v>I-00296</v>
+      </c>
+      <c r="H327" t="str">
         <f>アイテム項目!$F322</f>
-        <v>0</v>
+        <v>白色 歯ブラシ</v>
       </c>
       <c r="I327">
         <f>アイテム項目!$G322</f>
@@ -19799,21 +20108,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C328,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E328">
+      <c r="E328" t="str">
         <f>アイテム項目!$A323</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F328" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E328,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G328">
+      <c r="G328" t="str">
         <f>アイテム項目!$E323</f>
-        <v>0</v>
-      </c>
-      <c r="H328">
+        <v>I-00297</v>
+      </c>
+      <c r="H328" t="str">
         <f>アイテム項目!$F323</f>
-        <v>0</v>
+        <v>カッターナイフ</v>
       </c>
       <c r="I328">
         <f>アイテム項目!$G323</f>
@@ -19845,21 +20154,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C329,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E329">
+      <c r="E329" t="str">
         <f>アイテム項目!$A324</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F329" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E329,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G329">
+      <c r="G329" t="str">
         <f>アイテム項目!$E324</f>
-        <v>0</v>
-      </c>
-      <c r="H329">
+        <v>I-00298</v>
+      </c>
+      <c r="H329" t="str">
         <f>アイテム項目!$F324</f>
-        <v>0</v>
+        <v>黒 ボールペン</v>
       </c>
       <c r="I329">
         <f>アイテム項目!$G324</f>
@@ -19891,21 +20200,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C330,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E330">
+      <c r="E330" t="str">
         <f>アイテム項目!$A325</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F330" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E330,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G330">
+      <c r="G330" t="str">
         <f>アイテム項目!$E325</f>
-        <v>0</v>
-      </c>
-      <c r="H330">
+        <v>I-00299</v>
+      </c>
+      <c r="H330" t="str">
         <f>アイテム項目!$F325</f>
-        <v>0</v>
+        <v>グレー ペン</v>
       </c>
       <c r="I330">
         <f>アイテム項目!$G325</f>
@@ -19937,21 +20246,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C331,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E331">
+      <c r="E331" t="str">
         <f>アイテム項目!$A326</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F331" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E331,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G331">
+      <c r="G331" t="str">
         <f>アイテム項目!$E326</f>
-        <v>0</v>
-      </c>
-      <c r="H331">
+        <v>I-00300</v>
+      </c>
+      <c r="H331" t="str">
         <f>アイテム項目!$F326</f>
-        <v>0</v>
+        <v>白 ハサミ</v>
       </c>
       <c r="I331">
         <f>アイテム項目!$G326</f>
@@ -19983,21 +20292,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C332,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E332">
+      <c r="E332" t="str">
         <f>アイテム項目!$A327</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F332" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E332,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G332">
+      <c r="G332" t="str">
         <f>アイテム項目!$E327</f>
-        <v>0</v>
-      </c>
-      <c r="H332">
+        <v>I-00301</v>
+      </c>
+      <c r="H332" t="str">
         <f>アイテム項目!$F327</f>
-        <v>0</v>
+        <v>緑 指サック 5個入</v>
       </c>
       <c r="I332">
         <f>アイテム項目!$G327</f>
@@ -20029,21 +20338,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C333,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E333">
+      <c r="E333" t="str">
         <f>アイテム項目!$A328</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F333" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E333,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G333">
+      <c r="G333" t="str">
         <f>アイテム項目!$E328</f>
-        <v>0</v>
-      </c>
-      <c r="H333">
+        <v>I-00302</v>
+      </c>
+      <c r="H333" t="str">
         <f>アイテム項目!$F328</f>
-        <v>0</v>
+        <v>ホッチキス</v>
       </c>
       <c r="I333">
         <f>アイテム項目!$G328</f>
@@ -20075,21 +20384,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C334,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E334">
+      <c r="E334" t="str">
         <f>アイテム項目!$A329</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F334" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E334,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G334">
+      <c r="G334" t="str">
         <f>アイテム項目!$E329</f>
-        <v>0</v>
-      </c>
-      <c r="H334">
+        <v>I-00303</v>
+      </c>
+      <c r="H334" t="str">
         <f>アイテム項目!$F329</f>
-        <v>0</v>
+        <v>黒 テープ</v>
       </c>
       <c r="I334">
         <f>アイテム項目!$G329</f>
@@ -20121,21 +20430,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C335,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E335">
+      <c r="E335" t="str">
         <f>アイテム項目!$A330</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F335" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E335,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G335">
+      <c r="G335" t="str">
         <f>アイテム項目!$E330</f>
-        <v>0</v>
-      </c>
-      <c r="H335">
+        <v>I-00304</v>
+      </c>
+      <c r="H335" t="str">
         <f>アイテム項目!$F330</f>
-        <v>0</v>
+        <v>超強力両面テープ</v>
       </c>
       <c r="I335">
         <f>アイテム項目!$G330</f>
@@ -20167,21 +20476,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C336,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E336">
+      <c r="E336" t="str">
         <f>アイテム項目!$A331</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F336" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E336,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G336">
+      <c r="G336" t="str">
         <f>アイテム項目!$E331</f>
-        <v>0</v>
-      </c>
-      <c r="H336">
+        <v>I-00305</v>
+      </c>
+      <c r="H336" t="str">
         <f>アイテム項目!$F331</f>
-        <v>0</v>
+        <v>30cm 定規</v>
       </c>
       <c r="I336">
         <f>アイテム項目!$G331</f>
@@ -20213,21 +20522,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C337,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E337">
+      <c r="E337" t="str">
         <f>アイテム項目!$A332</f>
-        <v>0</v>
+        <v>T-0203</v>
       </c>
       <c r="F337" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E337,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G337">
+      <c r="G337" t="str">
         <f>アイテム項目!$E332</f>
-        <v>0</v>
-      </c>
-      <c r="H337">
+        <v>I-00306</v>
+      </c>
+      <c r="H337" t="str">
         <f>アイテム項目!$F332</f>
-        <v>0</v>
+        <v>クリップ</v>
       </c>
       <c r="I337">
         <f>アイテム項目!$G332</f>
@@ -20259,21 +20568,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C338,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E338">
+      <c r="E338" t="str">
         <f>アイテム項目!$A333</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F338" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E338,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G338">
+      <c r="G338" t="str">
         <f>アイテム項目!$E333</f>
-        <v>0</v>
-      </c>
-      <c r="H338">
+        <v>I-00307</v>
+      </c>
+      <c r="H338" t="str">
         <f>アイテム項目!$F333</f>
-        <v>0</v>
+        <v>ステレオイヤホン リール式</v>
       </c>
       <c r="I338">
         <f>アイテム項目!$G333</f>
@@ -20305,21 +20614,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C339,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E339">
+      <c r="E339" t="str">
         <f>アイテム項目!$A334</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F339" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E339,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G339">
+      <c r="G339" t="str">
         <f>アイテム項目!$E334</f>
-        <v>0</v>
-      </c>
-      <c r="H339">
+        <v>I-00308</v>
+      </c>
+      <c r="H339" t="str">
         <f>アイテム項目!$F334</f>
-        <v>0</v>
+        <v>QianLi ツール袋</v>
       </c>
       <c r="I339">
         <f>アイテム項目!$G334</f>
@@ -20351,21 +20660,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C340,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E340">
+      <c r="E340" t="str">
         <f>アイテム項目!$A335</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F340" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E340,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G340">
+      <c r="G340" t="str">
         <f>アイテム項目!$E335</f>
-        <v>0</v>
-      </c>
-      <c r="H340">
+        <v>I-00309</v>
+      </c>
+      <c r="H340" t="str">
         <f>アイテム項目!$F335</f>
-        <v>0</v>
+        <v>サングラス</v>
       </c>
       <c r="I340">
         <f>アイテム項目!$G335</f>
@@ -20397,21 +20706,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C341,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E341">
+      <c r="E341" t="str">
         <f>アイテム項目!$A336</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F341" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E341,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G341">
+      <c r="G341" t="str">
         <f>アイテム項目!$E336</f>
-        <v>0</v>
-      </c>
-      <c r="H341">
+        <v>I-00310</v>
+      </c>
+      <c r="H341" t="str">
         <f>アイテム項目!$F336</f>
-        <v>0</v>
+        <v>リール付ストラップ</v>
       </c>
       <c r="I341">
         <f>アイテム項目!$G336</f>
@@ -20443,21 +20752,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C342,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E342">
+      <c r="E342" t="str">
         <f>アイテム項目!$A337</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F342" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E342,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G342">
+      <c r="G342" t="str">
         <f>アイテム項目!$E337</f>
-        <v>0</v>
-      </c>
-      <c r="H342">
+        <v>I-00311</v>
+      </c>
+      <c r="H342" t="str">
         <f>アイテム項目!$F337</f>
-        <v>0</v>
+        <v>maxell 単3乾電池</v>
       </c>
       <c r="I342">
         <f>アイテム項目!$G337</f>
@@ -20489,21 +20798,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C343,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E343">
+      <c r="E343" t="str">
         <f>アイテム項目!$A338</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F343" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E343,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G343">
+      <c r="G343" t="str">
         <f>アイテム項目!$E338</f>
-        <v>0</v>
-      </c>
-      <c r="H343">
+        <v>I-00312</v>
+      </c>
+      <c r="H343" t="str">
         <f>アイテム項目!$F338</f>
-        <v>0</v>
+        <v>QianLi iToor PLUS</v>
       </c>
       <c r="I343">
         <f>アイテム項目!$G338</f>
@@ -20535,21 +20844,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C344,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E344">
+      <c r="E344" t="str">
         <f>アイテム項目!$A339</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F344" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E344,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G344">
+      <c r="G344" t="str">
         <f>アイテム項目!$E339</f>
-        <v>0</v>
-      </c>
-      <c r="H344">
+        <v>I-00313</v>
+      </c>
+      <c r="H344" t="str">
         <f>アイテム項目!$F339</f>
-        <v>0</v>
+        <v>ボタン電池</v>
       </c>
       <c r="I344">
         <f>アイテム項目!$G339</f>
@@ -20581,21 +20890,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C345,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E345">
+      <c r="E345" t="str">
         <f>アイテム項目!$A340</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F345" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E345,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G345">
+      <c r="G345" t="str">
         <f>アイテム項目!$E340</f>
-        <v>0</v>
-      </c>
-      <c r="H345">
+        <v>I-00314</v>
+      </c>
+      <c r="H345" t="str">
         <f>アイテム項目!$F340</f>
-        <v>0</v>
+        <v>CPUチップ</v>
       </c>
       <c r="I345">
         <f>アイテム項目!$G340</f>
@@ -20627,21 +20936,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C346,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E346">
+      <c r="E346" t="str">
         <f>アイテム項目!$A341</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F346" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E346,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G346">
+      <c r="G346" t="str">
         <f>アイテム項目!$E341</f>
-        <v>0</v>
-      </c>
-      <c r="H346">
+        <v>I-00315</v>
+      </c>
+      <c r="H346" t="str">
         <f>アイテム項目!$F341</f>
-        <v>0</v>
+        <v>白いロープ</v>
       </c>
       <c r="I346">
         <f>アイテム項目!$G341</f>
@@ -20673,21 +20982,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C347,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E347">
+      <c r="E347" t="str">
         <f>アイテム項目!$A342</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F347" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E347,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G347">
+      <c r="G347" t="str">
         <f>アイテム項目!$E342</f>
-        <v>0</v>
-      </c>
-      <c r="H347">
+        <v>I-00316</v>
+      </c>
+      <c r="H347" t="str">
         <f>アイテム項目!$F342</f>
-        <v>0</v>
+        <v>バーコード付き袋</v>
       </c>
       <c r="I347">
         <f>アイテム項目!$G342</f>
@@ -20719,21 +21028,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C348,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E348">
+      <c r="E348" t="str">
         <f>アイテム項目!$A343</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F348" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E348,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G348">
+      <c r="G348" t="str">
         <f>アイテム項目!$E343</f>
-        <v>0</v>
-      </c>
-      <c r="H348">
+        <v>I-00317</v>
+      </c>
+      <c r="H348" t="str">
         <f>アイテム項目!$F343</f>
-        <v>0</v>
+        <v>目薬</v>
       </c>
       <c r="I348">
         <f>アイテム項目!$G343</f>
@@ -20765,21 +21074,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C349,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E349">
+      <c r="E349" t="str">
         <f>アイテム項目!$A344</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F349" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E349,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G349">
+      <c r="G349" t="str">
         <f>アイテム項目!$E344</f>
-        <v>0</v>
-      </c>
-      <c r="H349">
+        <v>I-00318</v>
+      </c>
+      <c r="H349" t="str">
         <f>アイテム項目!$F344</f>
-        <v>0</v>
+        <v>USB基板部品</v>
       </c>
       <c r="I349">
         <f>アイテム項目!$G344</f>
@@ -20811,21 +21120,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C350,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E350">
+      <c r="E350" t="str">
         <f>アイテム項目!$A345</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F350" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E350,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G350">
+      <c r="G350" t="str">
         <f>アイテム項目!$E345</f>
-        <v>0</v>
-      </c>
-      <c r="H350">
+        <v>I-00319</v>
+      </c>
+      <c r="H350" t="str">
         <f>アイテム項目!$F345</f>
-        <v>0</v>
+        <v>電子工作パーツ</v>
       </c>
       <c r="I350">
         <f>アイテム項目!$G345</f>
@@ -20857,21 +21166,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C351,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E351">
+      <c r="E351" t="str">
         <f>アイテム項目!$A346</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F351" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E351,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G351">
+      <c r="G351" t="str">
         <f>アイテム項目!$E346</f>
-        <v>0</v>
-      </c>
-      <c r="H351">
+        <v>I-00320</v>
+      </c>
+      <c r="H351" t="str">
         <f>アイテム項目!$F346</f>
-        <v>0</v>
+        <v>精密スプリング</v>
       </c>
       <c r="I351">
         <f>アイテム項目!$G346</f>
@@ -20903,21 +21212,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C352,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E352">
+      <c r="E352" t="str">
         <f>アイテム項目!$A347</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F352" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E352,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G352">
+      <c r="G352" t="str">
         <f>アイテム項目!$E347</f>
-        <v>0</v>
-      </c>
-      <c r="H352">
+        <v>I-00321</v>
+      </c>
+      <c r="H352" t="str">
         <f>アイテム項目!$F347</f>
-        <v>0</v>
+        <v>クリーニングブラシ</v>
       </c>
       <c r="I352">
         <f>アイテム項目!$G347</f>
@@ -20949,21 +21258,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C353,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E353">
+      <c r="E353" t="str">
         <f>アイテム項目!$A348</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F353" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E353,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G353">
+      <c r="G353" t="str">
         <f>アイテム項目!$E348</f>
-        <v>0</v>
-      </c>
-      <c r="H353">
+        <v>I-00322</v>
+      </c>
+      <c r="H353" t="str">
         <f>アイテム項目!$F348</f>
-        <v>0</v>
+        <v>ピンセット</v>
       </c>
       <c r="I353">
         <f>アイテム項目!$G348</f>
@@ -20995,21 +21304,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C354,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E354">
+      <c r="E354" t="str">
         <f>アイテム項目!$A349</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F354" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E354,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G354">
+      <c r="G354" t="str">
         <f>アイテム項目!$E349</f>
-        <v>0</v>
-      </c>
-      <c r="H354">
+        <v>I-00323</v>
+      </c>
+      <c r="H354" t="str">
         <f>アイテム項目!$F349</f>
-        <v>0</v>
+        <v>クリップ</v>
       </c>
       <c r="I354">
         <f>アイテム項目!$G349</f>
@@ -21041,21 +21350,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C355,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E355">
+      <c r="E355" t="str">
         <f>アイテム項目!$A350</f>
-        <v>0</v>
+        <v>T-0204</v>
       </c>
       <c r="F355" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E355,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G355">
+      <c r="G355" t="str">
         <f>アイテム項目!$E350</f>
-        <v>0</v>
-      </c>
-      <c r="H355">
+        <v>I-00324</v>
+      </c>
+      <c r="H355" t="str">
         <f>アイテム項目!$F350</f>
-        <v>0</v>
+        <v>ライター</v>
       </c>
       <c r="I355">
         <f>アイテム項目!$G350</f>
@@ -21087,21 +21396,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C356,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E356">
+      <c r="E356" t="str">
         <f>アイテム項目!$A351</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F356" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E356,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G356">
+      <c r="G356" t="str">
         <f>アイテム項目!$E351</f>
-        <v>0</v>
-      </c>
-      <c r="H356">
+        <v>I-00325</v>
+      </c>
+      <c r="H356" t="str">
         <f>アイテム項目!$F351</f>
-        <v>0</v>
+        <v>ウェットシート 備品</v>
       </c>
       <c r="I356">
         <f>アイテム項目!$G351</f>
@@ -21133,21 +21442,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C357,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E357">
+      <c r="E357" t="str">
         <f>アイテム項目!$A352</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F357" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E357,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G357">
+      <c r="G357" t="str">
         <f>アイテム項目!$E352</f>
-        <v>0</v>
-      </c>
-      <c r="H357">
+        <v>I-00326</v>
+      </c>
+      <c r="H357" t="str">
         <f>アイテム項目!$F352</f>
-        <v>0</v>
+        <v>ウェットシート Jet</v>
       </c>
       <c r="I357">
         <f>アイテム項目!$G352</f>
@@ -21179,21 +21488,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C358,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E358">
+      <c r="E358" t="str">
         <f>アイテム項目!$A353</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F358" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E358,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G358">
+      <c r="G358" t="str">
         <f>アイテム項目!$E353</f>
-        <v>0</v>
-      </c>
-      <c r="H358">
+        <v>I-00327</v>
+      </c>
+      <c r="H358" t="str">
         <f>アイテム項目!$F353</f>
-        <v>0</v>
+        <v>ウェットシート モニター</v>
       </c>
       <c r="I358">
         <f>アイテム項目!$G353</f>
@@ -21225,21 +21534,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C359,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E359">
+      <c r="E359" t="str">
         <f>アイテム項目!$A354</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F359" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E359,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G359">
+      <c r="G359" t="str">
         <f>アイテム項目!$E354</f>
-        <v>0</v>
-      </c>
-      <c r="H359">
+        <v>I-00328</v>
+      </c>
+      <c r="H359" t="str">
         <f>アイテム項目!$F354</f>
-        <v>0</v>
+        <v>ウェットシート 手前</v>
       </c>
       <c r="I359">
         <f>アイテム項目!$G354</f>
@@ -21271,21 +21580,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C360,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E360">
+      <c r="E360" t="str">
         <f>アイテム項目!$A355</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F360" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E360,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G360">
+      <c r="G360" t="str">
         <f>アイテム項目!$E355</f>
-        <v>0</v>
-      </c>
-      <c r="H360">
+        <v>I-00329</v>
+      </c>
+      <c r="H360" t="str">
         <f>アイテム項目!$F355</f>
-        <v>0</v>
+        <v>WATER BASED MARKER</v>
       </c>
       <c r="I360">
         <f>アイテム項目!$G355</f>
@@ -21317,21 +21626,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C361,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E361">
+      <c r="E361" t="str">
         <f>アイテム項目!$A356</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F361" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E361,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G361">
+      <c r="G361" t="str">
         <f>アイテム項目!$E356</f>
-        <v>0</v>
-      </c>
-      <c r="H361">
+        <v>I-00330</v>
+      </c>
+      <c r="H361" t="str">
         <f>アイテム項目!$F356</f>
-        <v>0</v>
+        <v>ピンク ハサミ</v>
       </c>
       <c r="I361">
         <f>アイテム項目!$G356</f>
@@ -21363,21 +21672,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C362,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E362">
+      <c r="E362" t="str">
         <f>アイテム項目!$A357</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F362" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E362,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G362">
+      <c r="G362" t="str">
         <f>アイテム項目!$E357</f>
-        <v>0</v>
-      </c>
-      <c r="H362">
+        <v>I-00331</v>
+      </c>
+      <c r="H362" t="str">
         <f>アイテム項目!$F357</f>
-        <v>0</v>
+        <v>ZEBRA 3色ボールペン</v>
       </c>
       <c r="I362">
         <f>アイテム項目!$G357</f>
@@ -21409,21 +21718,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C363,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E363">
+      <c r="E363" t="str">
         <f>アイテム項目!$A358</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F363" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E363,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G363">
+      <c r="G363" t="str">
         <f>アイテム項目!$E358</f>
-        <v>0</v>
-      </c>
-      <c r="H363">
+        <v>I-00332</v>
+      </c>
+      <c r="H363" t="str">
         <f>アイテム項目!$F358</f>
-        <v>0</v>
+        <v>ENERGEL ア souvenir</v>
       </c>
       <c r="I363">
         <f>アイテム項目!$G358</f>
@@ -21455,21 +21764,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C364,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E364">
+      <c r="E364" t="str">
         <f>アイテム項目!$A359</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F364" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E364,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G364">
+      <c r="G364" t="str">
         <f>アイテム項目!$E359</f>
-        <v>0</v>
-      </c>
-      <c r="H364">
+        <v>I-00333</v>
+      </c>
+      <c r="H364" t="str">
         <f>アイテム項目!$F359</f>
-        <v>0</v>
+        <v>PILOT 消しゴム</v>
       </c>
       <c r="I364">
         <f>アイテム項目!$G359</f>
@@ -21501,21 +21810,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C365,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E365">
+      <c r="E365" t="str">
         <f>アイテム項目!$A360</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F365" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E365,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G365">
+      <c r="G365" t="str">
         <f>アイテム項目!$E360</f>
-        <v>0</v>
-      </c>
-      <c r="H365">
+        <v>I-00334</v>
+      </c>
+      <c r="H365" t="str">
         <f>アイテム項目!$F360</f>
-        <v>0</v>
+        <v>青 ボールペン</v>
       </c>
       <c r="I365">
         <f>アイテム項目!$G360</f>
@@ -21547,21 +21856,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C366,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E366">
+      <c r="E366" t="str">
         <f>アイテム項目!$A361</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F366" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E366,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G366">
+      <c r="G366" t="str">
         <f>アイテム項目!$E361</f>
-        <v>0</v>
-      </c>
-      <c r="H366">
+        <v>I-00335</v>
+      </c>
+      <c r="H366" t="str">
         <f>アイテム項目!$F361</f>
-        <v>0</v>
+        <v>白 ボールペン</v>
       </c>
       <c r="I366">
         <f>アイテム項目!$G361</f>
@@ -21593,21 +21902,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C367,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E367">
+      <c r="E367" t="str">
         <f>アイテム項目!$A362</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F367" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E367,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G367">
+      <c r="G367" t="str">
         <f>アイテム項目!$E362</f>
-        <v>0</v>
-      </c>
-      <c r="H367">
+        <v>I-00336</v>
+      </c>
+      <c r="H367" t="str">
         <f>アイテム項目!$F362</f>
-        <v>0</v>
+        <v>黄色 マーカーペン</v>
       </c>
       <c r="I367">
         <f>アイテム項目!$G362</f>
@@ -21639,21 +21948,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C368,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E368">
+      <c r="E368" t="str">
         <f>アイテム項目!$A363</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F368" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E368,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G368">
+      <c r="G368" t="str">
         <f>アイテム項目!$E363</f>
-        <v>0</v>
-      </c>
-      <c r="H368">
+        <v>I-00337</v>
+      </c>
+      <c r="H368" t="str">
         <f>アイテム項目!$F363</f>
-        <v>0</v>
+        <v>赤 マーカーペン</v>
       </c>
       <c r="I368">
         <f>アイテム項目!$G363</f>
@@ -21685,21 +21994,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C369,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E369">
+      <c r="E369" t="str">
         <f>アイテム項目!$A364</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F369" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E369,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G369">
+      <c r="G369" t="str">
         <f>アイテム項目!$E364</f>
-        <v>0</v>
-      </c>
-      <c r="H369">
+        <v>I-00338</v>
+      </c>
+      <c r="H369" t="str">
         <f>アイテム項目!$F364</f>
-        <v>0</v>
+        <v>黒 シャープペン</v>
       </c>
       <c r="I369">
         <f>アイテム項目!$G364</f>
@@ -21731,21 +22040,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C370,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E370">
+      <c r="E370" t="str">
         <f>アイテム項目!$A365</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F370" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E370,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G370">
+      <c r="G370" t="str">
         <f>アイテム項目!$E365</f>
-        <v>0</v>
-      </c>
-      <c r="H370">
+        <v>I-00339</v>
+      </c>
+      <c r="H370" t="str">
         <f>アイテム項目!$F365</f>
-        <v>0</v>
+        <v>ビニール袋入りアイテム</v>
       </c>
       <c r="I370">
         <f>アイテム項目!$G365</f>
@@ -21777,21 +22086,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C371,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E371">
+      <c r="E371" t="str">
         <f>アイテム項目!$A366</f>
-        <v>0</v>
+        <v>T-0205</v>
       </c>
       <c r="F371" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E371,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G371">
+      <c r="G371" t="str">
         <f>アイテム項目!$E366</f>
-        <v>0</v>
-      </c>
-      <c r="H371">
+        <v>I-00340</v>
+      </c>
+      <c r="H371" t="str">
         <f>アイテム項目!$F366</f>
-        <v>0</v>
+        <v>カラフル インデックス</v>
       </c>
       <c r="I371">
         <f>アイテム項目!$G366</f>
@@ -55079,7 +55388,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:L314"/>
+  <dimension ref="A1:L366"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
@@ -62477,6 +62786,1046 @@
       </c>
       <c r="I314" t="s">
         <v>1172</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11">
+      <c r="A315" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B315" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C315" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E315" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F315" s="29" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11">
+      <c r="A316" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B316" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C316" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E316" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F316" s="29" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11">
+      <c r="A317" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B317" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C317" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D317" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E317" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F317" s="29" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11">
+      <c r="A318" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B318" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C318" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E318" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F318" s="29" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11">
+      <c r="A319" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B319" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C319" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E319" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F319" s="29" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11">
+      <c r="A320" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B320" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C320" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E320" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F320" s="29" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B321" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C321" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E321" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F321" s="29" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B322" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C322" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D322" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E322" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F322" s="29" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B323" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C323" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E323" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F323" s="29" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B324" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C324" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E324" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F324" s="29" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B325" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C325" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D325" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F325" s="29" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B326" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C326" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D326" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E326" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F326" s="29" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B327" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C327" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D327" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E327" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F327" s="29" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B328" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C328" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D328" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E328" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F328" s="29" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B329" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C329" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E329" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F329" s="29" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B330" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C330" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D330" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E330" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F330" s="29" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B331" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C331" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D331" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E331" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F331" s="29" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B332" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C332" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D332" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E332" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F332" s="29" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B333" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C333" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E333" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F333" s="29" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B334" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F334" s="29" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B335" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C335" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F335" s="29" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B336" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C336" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D336" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F336" s="29" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B337" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C337" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D337" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F337" s="29" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B338" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C338" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D338" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F338" s="29" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B339" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C339" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D339" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F339" s="29" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B340" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C340" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D340" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E340" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F340" s="29" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B341" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C341" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D341" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E341" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F341" s="29" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B342" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C342" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D342" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F342" s="29" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B343" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C343" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D343" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F343" s="29" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B344" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C344" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D344" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F344" s="29" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B345" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C345" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D345" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F345" s="29" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B346" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C346" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D346" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F346" s="29" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B347" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C347" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D347" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F347" s="29" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B348" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C348" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D348" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F348" s="29" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B349" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C349" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D349" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F349" s="29" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B350" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C350" s="29" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D350" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F350" s="29" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B351" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C351" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D351" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E351" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F351" s="29" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B352" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C352" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D352" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F352" s="29" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B353" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C353" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D353" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F353" s="29" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B354" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C354" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D354" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F354" s="29" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B355" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C355" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D355" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F355" s="29" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B356" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C356" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D356" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F356" s="29" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B357" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C357" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D357" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E357" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F357" s="29" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B358" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C358" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F358" s="29" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B359" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C359" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D359" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E359" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F359" s="29" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B360" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C360" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F360" s="29" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B361" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C361" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D361" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E361" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F361" s="29" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B362" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C362" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D362" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E362" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F362" s="29" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B363" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C363" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D363" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F363" s="29" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B364" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C364" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D364" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E364" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F364" s="29" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B365" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C365" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D365" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E365" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F365" s="29" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B366" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C366" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D366" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E366" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F366" s="29" t="s">
+        <v>1275</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AF0D2C-7329-475B-A223-73C8C5C3798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2488B69-D891-4E6A-A60D-4237F24C2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="1860" windowWidth="16155" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="1860" windowWidth="16155" windowHeight="13275" tabRatio="901" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67EB6A2-B3DF-4DF3-AE1C-B78514569D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB319B4-1183-41FE-A4FA-1A83398BED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="2670" windowWidth="22170" windowHeight="13275" tabRatio="901" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13695" yWindow="2010" windowWidth="14730" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="1376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="1472">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -4166,6 +4166,305 @@
   </si>
   <si>
     <t>ゴミ箱として使用</t>
+  </si>
+  <si>
+    <t>I-00337</t>
+  </si>
+  <si>
+    <t>I-00338</t>
+  </si>
+  <si>
+    <t>I-00339</t>
+  </si>
+  <si>
+    <t>I-00340</t>
+  </si>
+  <si>
+    <t>I-00341</t>
+  </si>
+  <si>
+    <t>I-00342</t>
+  </si>
+  <si>
+    <t>I-00343</t>
+  </si>
+  <si>
+    <t>I-00344</t>
+  </si>
+  <si>
+    <t>I-00345</t>
+  </si>
+  <si>
+    <t>I-00346</t>
+  </si>
+  <si>
+    <t>I-00347</t>
+  </si>
+  <si>
+    <t>I-00348</t>
+  </si>
+  <si>
+    <t>I-00349</t>
+  </si>
+  <si>
+    <t>I-00350</t>
+  </si>
+  <si>
+    <t>I-00351</t>
+  </si>
+  <si>
+    <t>I-00352</t>
+  </si>
+  <si>
+    <t>コンクリートタガネ（小）</t>
+  </si>
+  <si>
+    <t>I-00353</t>
+  </si>
+  <si>
+    <t>I-00354</t>
+  </si>
+  <si>
+    <t>30cm差し金（L字定規）</t>
+  </si>
+  <si>
+    <t>I-00355</t>
+  </si>
+  <si>
+    <t>I-00356</t>
+  </si>
+  <si>
+    <t>I-00357</t>
+  </si>
+  <si>
+    <t>プリセット型トルクレンチ</t>
+  </si>
+  <si>
+    <t>I-00358</t>
+  </si>
+  <si>
+    <t>I-00359</t>
+  </si>
+  <si>
+    <t>ミニラジオペンチ 青</t>
+  </si>
+  <si>
+    <t>コンビネーションハンマー 黄黒</t>
+  </si>
+  <si>
+    <t>ペンチ（サビあり） オレンジ黒</t>
+  </si>
+  <si>
+    <t>電工ペンチ 黄黒</t>
+  </si>
+  <si>
+    <t>ニッパー 黒</t>
+  </si>
+  <si>
+    <t>ペンチ 赤黒</t>
+  </si>
+  <si>
+    <t>ミニラジオペンチ オレンジ黒</t>
+  </si>
+  <si>
+    <t>ラジオペンチ 紫</t>
+  </si>
+  <si>
+    <t>先曲がりラジオペンチ 黄</t>
+  </si>
+  <si>
+    <t>ニッパー 黄緑</t>
+  </si>
+  <si>
+    <t>ワイヤーストリッパー FUJIYA オレンジ</t>
+  </si>
+  <si>
+    <t>貫通ドライバー プラス（大） 赤黒</t>
+  </si>
+  <si>
+    <t>マイナスドライバー 白黒</t>
+  </si>
+  <si>
+    <t>ドライバー プラス 赤黒</t>
+  </si>
+  <si>
+    <t>マイナスドライバー（小） 赤黒</t>
+  </si>
+  <si>
+    <t>コンデンサ型ドライバー 青</t>
+  </si>
+  <si>
+    <t>プラスチックノギス 白</t>
+  </si>
+  <si>
+    <t>ステンレス高級定規 30cm</t>
+  </si>
+  <si>
+    <t>トルクレンチ用プラスチックケース 黒</t>
+  </si>
+  <si>
+    <t>精密ニッパー 黄黒</t>
+  </si>
+  <si>
+    <t>I-00360</t>
+  </si>
+  <si>
+    <t>絶縁ビニールテープ 黒</t>
+  </si>
+  <si>
+    <t>I-00361</t>
+  </si>
+  <si>
+    <t>ハサミ 緑</t>
+  </si>
+  <si>
+    <t>I-00362</t>
+  </si>
+  <si>
+    <t>圧着工具プライヤー</t>
+  </si>
+  <si>
+    <t>I-00363</t>
+  </si>
+  <si>
+    <t>ネジロック剤（瞬間接着剤）チューブ</t>
+  </si>
+  <si>
+    <t>I-00364</t>
+  </si>
+  <si>
+    <t>ミニカッター 白</t>
+  </si>
+  <si>
+    <t>I-00365</t>
+  </si>
+  <si>
+    <t>L字六角レンチ・ソケットビット各種</t>
+  </si>
+  <si>
+    <t>I-00366</t>
+  </si>
+  <si>
+    <t>片口スパナ・両口スパナ各種</t>
+  </si>
+  <si>
+    <t>I-00367</t>
+  </si>
+  <si>
+    <t>丸型ミニヤスリ</t>
+  </si>
+  <si>
+    <t>I-00368</t>
+  </si>
+  <si>
+    <t>ミニ切断砥石・軸付パーツ</t>
+  </si>
+  <si>
+    <t>I-00369</t>
+  </si>
+  <si>
+    <t>差し替え精密ドライバー 黒</t>
+  </si>
+  <si>
+    <t>I-00370</t>
+  </si>
+  <si>
+    <t>サンドペーパー各種</t>
+  </si>
+  <si>
+    <t>I-00371</t>
+  </si>
+  <si>
+    <t>I-00372</t>
+  </si>
+  <si>
+    <t>スナップリングプライヤー 黒</t>
+  </si>
+  <si>
+    <t>I-00373</t>
+  </si>
+  <si>
+    <t>六角レンチ棒各種セット（ホルダー入）</t>
+  </si>
+  <si>
+    <t>I-00374</t>
+  </si>
+  <si>
+    <t>両口スパナ（大） 黒</t>
+  </si>
+  <si>
+    <t>I-00375</t>
+  </si>
+  <si>
+    <t>マイナスドライバー 青白</t>
+  </si>
+  <si>
+    <t>I-00376</t>
+  </si>
+  <si>
+    <t>I-00377</t>
+  </si>
+  <si>
+    <t>精密ドライバー プラス 赤黒</t>
+  </si>
+  <si>
+    <t>I-00378</t>
+  </si>
+  <si>
+    <t>ドライバー マイナス 赤黒</t>
+  </si>
+  <si>
+    <t>I-00379</t>
+  </si>
+  <si>
+    <t>平細ヤスリ オレンジ</t>
+  </si>
+  <si>
+    <t>I-00380</t>
+  </si>
+  <si>
+    <t>モンキーレンチ（中） シルバー</t>
+  </si>
+  <si>
+    <t>I-00381</t>
+  </si>
+  <si>
+    <t>両口メガネレンチ（小） 5.5×7</t>
+  </si>
+  <si>
+    <t>I-00382</t>
+  </si>
+  <si>
+    <t>両口メガネレンチ（中）</t>
+  </si>
+  <si>
+    <t>I-00383</t>
+  </si>
+  <si>
+    <t>モーターレンチ（フックレンチ風）</t>
+  </si>
+  <si>
+    <t>I-00384</t>
+  </si>
+  <si>
+    <t>Cordless Screwdriver 電動ドライバーセット（白黒・ケース入）</t>
+  </si>
+  <si>
+    <t>パーツケース上（専用ケース）</t>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルミ針金（巻）</t>
+    <rPh sb="3" eb="5">
+      <t>ハリガネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -21430,43 +21729,43 @@
     <row r="351" spans="1:11">
       <c r="A351" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C351,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B351" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A351,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C351" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E351,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D351" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C351,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E351">
+        <v>左底面</v>
+      </c>
+      <c r="E351" t="str">
         <f>アイテム項目!$A351</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F351" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E351,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G351">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G351" t="str">
         <f>アイテム項目!$E351</f>
-        <v>0</v>
-      </c>
-      <c r="H351">
+        <v>I-00337</v>
+      </c>
+      <c r="H351" t="str">
         <f>アイテム項目!$F351</f>
-        <v>0</v>
-      </c>
-      <c r="I351">
+        <v>ミニラジオペンチ 青</v>
+      </c>
+      <c r="I351" t="str">
         <f>アイテム項目!$G351</f>
-        <v>0</v>
-      </c>
-      <c r="J351">
+        <v>工具</v>
+      </c>
+      <c r="J351" t="str">
         <f>アイテム項目!$H351</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K351">
         <f>アイテム項目!$I351</f>
@@ -21476,43 +21775,43 @@
     <row r="352" spans="1:11">
       <c r="A352" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C352,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B352" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A352,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C352" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E352,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D352" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C352,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E352">
+        <v>左底面</v>
+      </c>
+      <c r="E352" t="str">
         <f>アイテム項目!$A352</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F352" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E352,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G352">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G352" t="str">
         <f>アイテム項目!$E352</f>
-        <v>0</v>
-      </c>
-      <c r="H352">
+        <v>I-00338</v>
+      </c>
+      <c r="H352" t="str">
         <f>アイテム項目!$F352</f>
-        <v>0</v>
-      </c>
-      <c r="I352">
+        <v>コンビネーションハンマー 黄黒</v>
+      </c>
+      <c r="I352" t="str">
         <f>アイテム項目!$G352</f>
-        <v>0</v>
-      </c>
-      <c r="J352">
+        <v>工具</v>
+      </c>
+      <c r="J352" t="str">
         <f>アイテム項目!$H352</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K352">
         <f>アイテム項目!$I352</f>
@@ -21522,43 +21821,43 @@
     <row r="353" spans="1:11">
       <c r="A353" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C353,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B353" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A353,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C353" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E353,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D353" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C353,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E353">
+        <v>左底面</v>
+      </c>
+      <c r="E353" t="str">
         <f>アイテム項目!$A353</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F353" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E353,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G353">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G353" t="str">
         <f>アイテム項目!$E353</f>
-        <v>0</v>
-      </c>
-      <c r="H353">
+        <v>I-00339</v>
+      </c>
+      <c r="H353" t="str">
         <f>アイテム項目!$F353</f>
-        <v>0</v>
-      </c>
-      <c r="I353">
+        <v>ペンチ（サビあり） オレンジ黒</v>
+      </c>
+      <c r="I353" t="str">
         <f>アイテム項目!$G353</f>
-        <v>0</v>
-      </c>
-      <c r="J353">
+        <v>工具</v>
+      </c>
+      <c r="J353" t="str">
         <f>アイテム項目!$H353</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K353">
         <f>アイテム項目!$I353</f>
@@ -21568,43 +21867,43 @@
     <row r="354" spans="1:11">
       <c r="A354" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C354,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B354" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A354,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C354" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E354,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D354" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C354,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E354">
+        <v>左底面</v>
+      </c>
+      <c r="E354" t="str">
         <f>アイテム項目!$A354</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F354" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E354,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G354">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G354" t="str">
         <f>アイテム項目!$E354</f>
-        <v>0</v>
-      </c>
-      <c r="H354">
+        <v>I-00340</v>
+      </c>
+      <c r="H354" t="str">
         <f>アイテム項目!$F354</f>
-        <v>0</v>
-      </c>
-      <c r="I354">
+        <v>電工ペンチ 黄黒</v>
+      </c>
+      <c r="I354" t="str">
         <f>アイテム項目!$G354</f>
-        <v>0</v>
-      </c>
-      <c r="J354">
+        <v>工具</v>
+      </c>
+      <c r="J354" t="str">
         <f>アイテム項目!$H354</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K354">
         <f>アイテム項目!$I354</f>
@@ -21614,43 +21913,43 @@
     <row r="355" spans="1:11">
       <c r="A355" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C355,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B355" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A355,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C355" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E355,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D355" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C355,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E355">
+        <v>左底面</v>
+      </c>
+      <c r="E355" t="str">
         <f>アイテム項目!$A355</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F355" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E355,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G355">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G355" t="str">
         <f>アイテム項目!$E355</f>
-        <v>0</v>
-      </c>
-      <c r="H355">
+        <v>I-00341</v>
+      </c>
+      <c r="H355" t="str">
         <f>アイテム項目!$F355</f>
-        <v>0</v>
-      </c>
-      <c r="I355">
+        <v>ニッパー 黒</v>
+      </c>
+      <c r="I355" t="str">
         <f>アイテム項目!$G355</f>
-        <v>0</v>
-      </c>
-      <c r="J355">
+        <v>工具</v>
+      </c>
+      <c r="J355" t="str">
         <f>アイテム項目!$H355</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K355">
         <f>アイテム項目!$I355</f>
@@ -21660,43 +21959,43 @@
     <row r="356" spans="1:11">
       <c r="A356" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C356,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B356" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A356,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C356" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E356,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D356" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C356,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E356">
+        <v>左底面</v>
+      </c>
+      <c r="E356" t="str">
         <f>アイテム項目!$A356</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F356" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E356,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G356">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G356" t="str">
         <f>アイテム項目!$E356</f>
-        <v>0</v>
-      </c>
-      <c r="H356">
+        <v>I-00342</v>
+      </c>
+      <c r="H356" t="str">
         <f>アイテム項目!$F356</f>
-        <v>0</v>
-      </c>
-      <c r="I356">
+        <v>ペンチ 赤黒</v>
+      </c>
+      <c r="I356" t="str">
         <f>アイテム項目!$G356</f>
-        <v>0</v>
-      </c>
-      <c r="J356">
+        <v>工具</v>
+      </c>
+      <c r="J356" t="str">
         <f>アイテム項目!$H356</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K356">
         <f>アイテム項目!$I356</f>
@@ -21706,43 +22005,43 @@
     <row r="357" spans="1:11">
       <c r="A357" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C357,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B357" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A357,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C357" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E357,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D357" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C357,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E357">
+        <v>左底面</v>
+      </c>
+      <c r="E357" t="str">
         <f>アイテム項目!$A357</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F357" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E357,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G357">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G357" t="str">
         <f>アイテム項目!$E357</f>
-        <v>0</v>
-      </c>
-      <c r="H357">
+        <v>I-00343</v>
+      </c>
+      <c r="H357" t="str">
         <f>アイテム項目!$F357</f>
-        <v>0</v>
-      </c>
-      <c r="I357">
+        <v>ミニラジオペンチ オレンジ黒</v>
+      </c>
+      <c r="I357" t="str">
         <f>アイテム項目!$G357</f>
-        <v>0</v>
-      </c>
-      <c r="J357">
+        <v>工具</v>
+      </c>
+      <c r="J357" t="str">
         <f>アイテム項目!$H357</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K357">
         <f>アイテム項目!$I357</f>
@@ -21752,43 +22051,43 @@
     <row r="358" spans="1:11">
       <c r="A358" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C358,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B358" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A358,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C358" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E358,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D358" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C358,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E358">
+        <v>左底面</v>
+      </c>
+      <c r="E358" t="str">
         <f>アイテム項目!$A358</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F358" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E358,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G358">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G358" t="str">
         <f>アイテム項目!$E358</f>
-        <v>0</v>
-      </c>
-      <c r="H358">
+        <v>I-00344</v>
+      </c>
+      <c r="H358" t="str">
         <f>アイテム項目!$F358</f>
-        <v>0</v>
-      </c>
-      <c r="I358">
+        <v>ラジオペンチ 紫</v>
+      </c>
+      <c r="I358" t="str">
         <f>アイテム項目!$G358</f>
-        <v>0</v>
-      </c>
-      <c r="J358">
+        <v>工具</v>
+      </c>
+      <c r="J358" t="str">
         <f>アイテム項目!$H358</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K358">
         <f>アイテム項目!$I358</f>
@@ -21798,43 +22097,43 @@
     <row r="359" spans="1:11">
       <c r="A359" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C359,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B359" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A359,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C359" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E359,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D359" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C359,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E359">
+        <v>左底面</v>
+      </c>
+      <c r="E359" t="str">
         <f>アイテム項目!$A359</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F359" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E359,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G359">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G359" t="str">
         <f>アイテム項目!$E359</f>
-        <v>0</v>
-      </c>
-      <c r="H359">
+        <v>I-00345</v>
+      </c>
+      <c r="H359" t="str">
         <f>アイテム項目!$F359</f>
-        <v>0</v>
-      </c>
-      <c r="I359">
+        <v>先曲がりラジオペンチ 黄</v>
+      </c>
+      <c r="I359" t="str">
         <f>アイテム項目!$G359</f>
-        <v>0</v>
-      </c>
-      <c r="J359">
+        <v>工具</v>
+      </c>
+      <c r="J359" t="str">
         <f>アイテム項目!$H359</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K359">
         <f>アイテム項目!$I359</f>
@@ -21844,43 +22143,43 @@
     <row r="360" spans="1:11">
       <c r="A360" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C360,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B360" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A360,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C360" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E360,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D360" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C360,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E360">
+        <v>左底面</v>
+      </c>
+      <c r="E360" t="str">
         <f>アイテム項目!$A360</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F360" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E360,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G360">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G360" t="str">
         <f>アイテム項目!$E360</f>
-        <v>0</v>
-      </c>
-      <c r="H360">
+        <v>I-00346</v>
+      </c>
+      <c r="H360" t="str">
         <f>アイテム項目!$F360</f>
-        <v>0</v>
-      </c>
-      <c r="I360">
+        <v>ニッパー 黄緑</v>
+      </c>
+      <c r="I360" t="str">
         <f>アイテム項目!$G360</f>
-        <v>0</v>
-      </c>
-      <c r="J360">
+        <v>工具</v>
+      </c>
+      <c r="J360" t="str">
         <f>アイテム項目!$H360</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K360">
         <f>アイテム項目!$I360</f>
@@ -21890,43 +22189,43 @@
     <row r="361" spans="1:11">
       <c r="A361" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C361,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B361" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A361,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C361" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E361,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D361" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C361,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E361">
+        <v>左底面</v>
+      </c>
+      <c r="E361" t="str">
         <f>アイテム項目!$A361</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F361" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E361,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G361">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G361" t="str">
         <f>アイテム項目!$E361</f>
-        <v>0</v>
-      </c>
-      <c r="H361">
+        <v>I-00347</v>
+      </c>
+      <c r="H361" t="str">
         <f>アイテム項目!$F361</f>
-        <v>0</v>
-      </c>
-      <c r="I361">
+        <v>ワイヤーストリッパー FUJIYA オレンジ</v>
+      </c>
+      <c r="I361" t="str">
         <f>アイテム項目!$G361</f>
-        <v>0</v>
-      </c>
-      <c r="J361">
+        <v>工具</v>
+      </c>
+      <c r="J361" t="str">
         <f>アイテム項目!$H361</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K361">
         <f>アイテム項目!$I361</f>
@@ -21936,43 +22235,43 @@
     <row r="362" spans="1:11">
       <c r="A362" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C362,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B362" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A362,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C362" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E362,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D362" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C362,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E362">
+        <v>左底面</v>
+      </c>
+      <c r="E362" t="str">
         <f>アイテム項目!$A362</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F362" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E362,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G362">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G362" t="str">
         <f>アイテム項目!$E362</f>
-        <v>0</v>
-      </c>
-      <c r="H362">
+        <v>I-00348</v>
+      </c>
+      <c r="H362" t="str">
         <f>アイテム項目!$F362</f>
-        <v>0</v>
-      </c>
-      <c r="I362">
+        <v>貫通ドライバー プラス（大） 赤黒</v>
+      </c>
+      <c r="I362" t="str">
         <f>アイテム項目!$G362</f>
-        <v>0</v>
-      </c>
-      <c r="J362">
+        <v>工具</v>
+      </c>
+      <c r="J362" t="str">
         <f>アイテム項目!$H362</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K362">
         <f>アイテム項目!$I362</f>
@@ -21982,43 +22281,43 @@
     <row r="363" spans="1:11">
       <c r="A363" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C363,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B363" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A363,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C363" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E363,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D363" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C363,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E363">
+        <v>左底面</v>
+      </c>
+      <c r="E363" t="str">
         <f>アイテム項目!$A363</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F363" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E363,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G363">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G363" t="str">
         <f>アイテム項目!$E363</f>
-        <v>0</v>
-      </c>
-      <c r="H363">
+        <v>I-00349</v>
+      </c>
+      <c r="H363" t="str">
         <f>アイテム項目!$F363</f>
-        <v>0</v>
-      </c>
-      <c r="I363">
+        <v>マイナスドライバー 白黒</v>
+      </c>
+      <c r="I363" t="str">
         <f>アイテム項目!$G363</f>
-        <v>0</v>
-      </c>
-      <c r="J363">
+        <v>工具</v>
+      </c>
+      <c r="J363" t="str">
         <f>アイテム項目!$H363</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K363">
         <f>アイテム項目!$I363</f>
@@ -22028,43 +22327,43 @@
     <row r="364" spans="1:11">
       <c r="A364" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C364,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B364" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A364,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C364" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E364,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D364" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C364,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E364">
+        <v>左底面</v>
+      </c>
+      <c r="E364" t="str">
         <f>アイテム項目!$A364</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F364" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E364,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G364">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G364" t="str">
         <f>アイテム項目!$E364</f>
-        <v>0</v>
-      </c>
-      <c r="H364">
+        <v>I-00350</v>
+      </c>
+      <c r="H364" t="str">
         <f>アイテム項目!$F364</f>
-        <v>0</v>
-      </c>
-      <c r="I364">
+        <v>ドライバー プラス 赤黒</v>
+      </c>
+      <c r="I364" t="str">
         <f>アイテム項目!$G364</f>
-        <v>0</v>
-      </c>
-      <c r="J364">
+        <v>工具</v>
+      </c>
+      <c r="J364" t="str">
         <f>アイテム項目!$H364</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K364">
         <f>アイテム項目!$I364</f>
@@ -22074,43 +22373,43 @@
     <row r="365" spans="1:11">
       <c r="A365" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C365,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B365" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A365,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C365" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E365,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D365" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C365,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E365">
+        <v>左底面</v>
+      </c>
+      <c r="E365" t="str">
         <f>アイテム項目!$A365</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F365" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E365,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G365">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G365" t="str">
         <f>アイテム項目!$E365</f>
-        <v>0</v>
-      </c>
-      <c r="H365">
+        <v>I-00351</v>
+      </c>
+      <c r="H365" t="str">
         <f>アイテム項目!$F365</f>
-        <v>0</v>
-      </c>
-      <c r="I365">
+        <v>マイナスドライバー（小） 赤黒</v>
+      </c>
+      <c r="I365" t="str">
         <f>アイテム項目!$G365</f>
-        <v>0</v>
-      </c>
-      <c r="J365">
+        <v>工具</v>
+      </c>
+      <c r="J365" t="str">
         <f>アイテム項目!$H365</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K365">
         <f>アイテム項目!$I365</f>
@@ -22120,43 +22419,43 @@
     <row r="366" spans="1:11">
       <c r="A366" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C366,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B366" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A366,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C366" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E366,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D366" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C366,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E366">
+        <v>左底面</v>
+      </c>
+      <c r="E366" t="str">
         <f>アイテム項目!$A366</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F366" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E366,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G366">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G366" t="str">
         <f>アイテム項目!$E366</f>
-        <v>0</v>
-      </c>
-      <c r="H366">
+        <v>I-00352</v>
+      </c>
+      <c r="H366" t="str">
         <f>アイテム項目!$F366</f>
-        <v>0</v>
-      </c>
-      <c r="I366">
+        <v>コンクリートタガネ（小）</v>
+      </c>
+      <c r="I366" t="str">
         <f>アイテム項目!$G366</f>
-        <v>0</v>
-      </c>
-      <c r="J366">
+        <v>工具</v>
+      </c>
+      <c r="J366" t="str">
         <f>アイテム項目!$H366</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K366">
         <f>アイテム項目!$I366</f>
@@ -22166,43 +22465,43 @@
     <row r="367" spans="1:11">
       <c r="A367" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C367,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B367" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A367,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C367" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E367,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D367" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C367,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E367">
+        <v>左底面</v>
+      </c>
+      <c r="E367" t="str">
         <f>アイテム項目!$A367</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F367" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E367,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G367">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G367" t="str">
         <f>アイテム項目!$E367</f>
-        <v>0</v>
-      </c>
-      <c r="H367">
+        <v>I-00353</v>
+      </c>
+      <c r="H367" t="str">
         <f>アイテム項目!$F367</f>
-        <v>0</v>
-      </c>
-      <c r="I367">
+        <v>コンデンサ型ドライバー 青</v>
+      </c>
+      <c r="I367" t="str">
         <f>アイテム項目!$G367</f>
-        <v>0</v>
-      </c>
-      <c r="J367">
+        <v>工具</v>
+      </c>
+      <c r="J367" t="str">
         <f>アイテム項目!$H367</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K367">
         <f>アイテム項目!$I367</f>
@@ -22212,43 +22511,43 @@
     <row r="368" spans="1:11">
       <c r="A368" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C368,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B368" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A368,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C368" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E368,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D368" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C368,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E368">
+        <v>左底面</v>
+      </c>
+      <c r="E368" t="str">
         <f>アイテム項目!$A368</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F368" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E368,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G368">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G368" t="str">
         <f>アイテム項目!$E368</f>
-        <v>0</v>
-      </c>
-      <c r="H368">
+        <v>I-00354</v>
+      </c>
+      <c r="H368" t="str">
         <f>アイテム項目!$F368</f>
-        <v>0</v>
-      </c>
-      <c r="I368">
+        <v>30cm差し金（L字定規）</v>
+      </c>
+      <c r="I368" t="str">
         <f>アイテム項目!$G368</f>
-        <v>0</v>
-      </c>
-      <c r="J368">
+        <v>工具</v>
+      </c>
+      <c r="J368" t="str">
         <f>アイテム項目!$H368</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K368">
         <f>アイテム項目!$I368</f>
@@ -22258,43 +22557,43 @@
     <row r="369" spans="1:11">
       <c r="A369" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C369,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B369" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A369,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C369" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E369,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D369" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C369,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E369">
+        <v>左底面</v>
+      </c>
+      <c r="E369" t="str">
         <f>アイテム項目!$A369</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F369" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E369,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G369">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G369" t="str">
         <f>アイテム項目!$E369</f>
-        <v>0</v>
-      </c>
-      <c r="H369">
+        <v>I-00355</v>
+      </c>
+      <c r="H369" t="str">
         <f>アイテム項目!$F369</f>
-        <v>0</v>
-      </c>
-      <c r="I369">
+        <v>プラスチックノギス 白</v>
+      </c>
+      <c r="I369" t="str">
         <f>アイテム項目!$G369</f>
-        <v>0</v>
-      </c>
-      <c r="J369">
+        <v>工具</v>
+      </c>
+      <c r="J369" t="str">
         <f>アイテム項目!$H369</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K369">
         <f>アイテム項目!$I369</f>
@@ -22304,43 +22603,43 @@
     <row r="370" spans="1:11">
       <c r="A370" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C370,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B370" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A370,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C370" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E370,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D370" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C370,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E370">
+        <v>左底面</v>
+      </c>
+      <c r="E370" t="str">
         <f>アイテム項目!$A370</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F370" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E370,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G370">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G370" t="str">
         <f>アイテム項目!$E370</f>
-        <v>0</v>
-      </c>
-      <c r="H370">
+        <v>I-00356</v>
+      </c>
+      <c r="H370" t="str">
         <f>アイテム項目!$F370</f>
-        <v>0</v>
-      </c>
-      <c r="I370">
+        <v>ステンレス高級定規 30cm</v>
+      </c>
+      <c r="I370" t="str">
         <f>アイテム項目!$G370</f>
-        <v>0</v>
-      </c>
-      <c r="J370">
+        <v>工具</v>
+      </c>
+      <c r="J370" t="str">
         <f>アイテム項目!$H370</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K370">
         <f>アイテム項目!$I370</f>
@@ -22350,43 +22649,43 @@
     <row r="371" spans="1:11">
       <c r="A371" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C371,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B371" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A371,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C371" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E371,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D371" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C371,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E371">
+        <v>左底面</v>
+      </c>
+      <c r="E371" t="str">
         <f>アイテム項目!$A371</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F371" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E371,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G371">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G371" t="str">
         <f>アイテム項目!$E371</f>
-        <v>0</v>
-      </c>
-      <c r="H371">
+        <v>I-00357</v>
+      </c>
+      <c r="H371" t="str">
         <f>アイテム項目!$F371</f>
-        <v>0</v>
-      </c>
-      <c r="I371">
+        <v>プリセット型トルクレンチ</v>
+      </c>
+      <c r="I371" t="str">
         <f>アイテム項目!$G371</f>
-        <v>0</v>
-      </c>
-      <c r="J371">
+        <v>工具</v>
+      </c>
+      <c r="J371" t="str">
         <f>アイテム項目!$H371</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K371">
         <f>アイテム項目!$I371</f>
@@ -22396,43 +22695,43 @@
     <row r="372" spans="1:11">
       <c r="A372" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C372,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B372" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A372,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C372" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E372,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D372" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C372,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E372">
+        <v>左底面</v>
+      </c>
+      <c r="E372" t="str">
         <f>アイテム項目!$A372</f>
-        <v>0</v>
+        <v>C-030401</v>
       </c>
       <c r="F372" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E372,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G372">
+        <v>工具キャリーバッグ（赤黒）</v>
+      </c>
+      <c r="G372" t="str">
         <f>アイテム項目!$E372</f>
-        <v>0</v>
-      </c>
-      <c r="H372">
+        <v>I-00358</v>
+      </c>
+      <c r="H372" t="str">
         <f>アイテム項目!$F372</f>
-        <v>0</v>
-      </c>
-      <c r="I372">
+        <v>トルクレンチ用プラスチックケース 黒</v>
+      </c>
+      <c r="I372" t="str">
         <f>アイテム項目!$G372</f>
-        <v>0</v>
-      </c>
-      <c r="J372">
+        <v>工具</v>
+      </c>
+      <c r="J372" t="str">
         <f>アイテム項目!$H372</f>
-        <v>0</v>
+        <v>B</v>
       </c>
       <c r="K372">
         <f>アイテム項目!$I372</f>
@@ -22488,43 +22787,43 @@
     <row r="374" spans="1:11">
       <c r="A374" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C374,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B374" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A374,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C374" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E374,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D374" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C374,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E374">
+        <v>左底面</v>
+      </c>
+      <c r="E374" t="str">
         <f>アイテム項目!$A374</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F374" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E374,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G374">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G374" t="str">
         <f>アイテム項目!$E374</f>
-        <v>0</v>
-      </c>
-      <c r="H374">
+        <v>I-00359</v>
+      </c>
+      <c r="H374" t="str">
         <f>アイテム項目!$F374</f>
-        <v>0</v>
-      </c>
-      <c r="I374">
+        <v>精密ニッパー 黄黒</v>
+      </c>
+      <c r="I374" t="str">
         <f>アイテム項目!$G374</f>
-        <v>0</v>
-      </c>
-      <c r="J374">
+        <v>工具</v>
+      </c>
+      <c r="J374" t="str">
         <f>アイテム項目!$H374</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K374">
         <f>アイテム項目!$I374</f>
@@ -22534,43 +22833,43 @@
     <row r="375" spans="1:11">
       <c r="A375" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C375,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B375" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A375,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C375" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E375,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D375" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C375,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E375">
+        <v>左底面</v>
+      </c>
+      <c r="E375" t="str">
         <f>アイテム項目!$A375</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F375" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E375,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G375">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G375" t="str">
         <f>アイテム項目!$E375</f>
-        <v>0</v>
-      </c>
-      <c r="H375">
+        <v>I-00360</v>
+      </c>
+      <c r="H375" t="str">
         <f>アイテム項目!$F375</f>
-        <v>0</v>
-      </c>
-      <c r="I375">
+        <v>絶縁ビニールテープ 黒</v>
+      </c>
+      <c r="I375" t="str">
         <f>アイテム項目!$G375</f>
-        <v>0</v>
-      </c>
-      <c r="J375">
+        <v>工具</v>
+      </c>
+      <c r="J375" t="str">
         <f>アイテム項目!$H375</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K375">
         <f>アイテム項目!$I375</f>
@@ -22580,43 +22879,43 @@
     <row r="376" spans="1:11">
       <c r="A376" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C376,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B376" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A376,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C376" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E376,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D376" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C376,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E376">
+        <v>左底面</v>
+      </c>
+      <c r="E376" t="str">
         <f>アイテム項目!$A376</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F376" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E376,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G376">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G376" t="str">
         <f>アイテム項目!$E376</f>
-        <v>0</v>
-      </c>
-      <c r="H376">
+        <v>I-00361</v>
+      </c>
+      <c r="H376" t="str">
         <f>アイテム項目!$F376</f>
-        <v>0</v>
-      </c>
-      <c r="I376">
+        <v>ハサミ 緑</v>
+      </c>
+      <c r="I376" t="str">
         <f>アイテム項目!$G376</f>
-        <v>0</v>
-      </c>
-      <c r="J376">
+        <v>工具</v>
+      </c>
+      <c r="J376" t="str">
         <f>アイテム項目!$H376</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K376">
         <f>アイテム項目!$I376</f>
@@ -22626,43 +22925,43 @@
     <row r="377" spans="1:11">
       <c r="A377" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C377,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B377" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A377,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C377" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E377,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D377" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C377,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E377">
+        <v>左底面</v>
+      </c>
+      <c r="E377" t="str">
         <f>アイテム項目!$A377</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F377" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E377,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G377">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G377" t="str">
         <f>アイテム項目!$E377</f>
-        <v>0</v>
-      </c>
-      <c r="H377">
+        <v>I-00362</v>
+      </c>
+      <c r="H377" t="str">
         <f>アイテム項目!$F377</f>
-        <v>0</v>
-      </c>
-      <c r="I377">
+        <v>圧着工具プライヤー</v>
+      </c>
+      <c r="I377" t="str">
         <f>アイテム項目!$G377</f>
-        <v>0</v>
-      </c>
-      <c r="J377">
+        <v>工具</v>
+      </c>
+      <c r="J377" t="str">
         <f>アイテム項目!$H377</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K377">
         <f>アイテム項目!$I377</f>
@@ -22672,43 +22971,43 @@
     <row r="378" spans="1:11">
       <c r="A378" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C378,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B378" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A378,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C378" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E378,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D378" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C378,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E378">
+        <v>左底面</v>
+      </c>
+      <c r="E378" t="str">
         <f>アイテム項目!$A378</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F378" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E378,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G378">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G378" t="str">
         <f>アイテム項目!$E378</f>
-        <v>0</v>
-      </c>
-      <c r="H378">
+        <v>I-00363</v>
+      </c>
+      <c r="H378" t="str">
         <f>アイテム項目!$F378</f>
-        <v>0</v>
-      </c>
-      <c r="I378">
+        <v>ネジロック剤（瞬間接着剤）チューブ</v>
+      </c>
+      <c r="I378" t="str">
         <f>アイテム項目!$G378</f>
-        <v>0</v>
-      </c>
-      <c r="J378">
+        <v>工具</v>
+      </c>
+      <c r="J378" t="str">
         <f>アイテム項目!$H378</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K378">
         <f>アイテム項目!$I378</f>
@@ -22718,43 +23017,43 @@
     <row r="379" spans="1:11">
       <c r="A379" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C379,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B379" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A379,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C379" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E379,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D379" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C379,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E379">
+        <v>左底面</v>
+      </c>
+      <c r="E379" t="str">
         <f>アイテム項目!$A379</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F379" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E379,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G379">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G379" t="str">
         <f>アイテム項目!$E379</f>
-        <v>0</v>
-      </c>
-      <c r="H379">
+        <v>I-00364</v>
+      </c>
+      <c r="H379" t="str">
         <f>アイテム項目!$F379</f>
-        <v>0</v>
-      </c>
-      <c r="I379">
+        <v>ミニカッター 白</v>
+      </c>
+      <c r="I379" t="str">
         <f>アイテム項目!$G379</f>
-        <v>0</v>
-      </c>
-      <c r="J379">
+        <v>工具</v>
+      </c>
+      <c r="J379" t="str">
         <f>アイテム項目!$H379</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K379">
         <f>アイテム項目!$I379</f>
@@ -22764,43 +23063,43 @@
     <row r="380" spans="1:11">
       <c r="A380" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C380,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B380" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A380,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C380" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E380,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D380" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C380,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E380">
+        <v>左底面</v>
+      </c>
+      <c r="E380" t="str">
         <f>アイテム項目!$A380</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F380" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E380,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G380">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G380" t="str">
         <f>アイテム項目!$E380</f>
-        <v>0</v>
-      </c>
-      <c r="H380">
+        <v>I-00365</v>
+      </c>
+      <c r="H380" t="str">
         <f>アイテム項目!$F380</f>
-        <v>0</v>
-      </c>
-      <c r="I380">
+        <v>L字六角レンチ・ソケットビット各種</v>
+      </c>
+      <c r="I380" t="str">
         <f>アイテム項目!$G380</f>
-        <v>0</v>
-      </c>
-      <c r="J380">
+        <v>工具</v>
+      </c>
+      <c r="J380" t="str">
         <f>アイテム項目!$H380</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K380">
         <f>アイテム項目!$I380</f>
@@ -22810,43 +23109,43 @@
     <row r="381" spans="1:11">
       <c r="A381" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C381,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B381" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A381,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C381" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E381,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D381" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C381,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E381">
+        <v>左底面</v>
+      </c>
+      <c r="E381" t="str">
         <f>アイテム項目!$A381</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F381" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E381,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G381">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G381" t="str">
         <f>アイテム項目!$E381</f>
-        <v>0</v>
-      </c>
-      <c r="H381">
+        <v>I-00366</v>
+      </c>
+      <c r="H381" t="str">
         <f>アイテム項目!$F381</f>
-        <v>0</v>
-      </c>
-      <c r="I381">
+        <v>片口スパナ・両口スパナ各種</v>
+      </c>
+      <c r="I381" t="str">
         <f>アイテム項目!$G381</f>
-        <v>0</v>
-      </c>
-      <c r="J381">
+        <v>工具</v>
+      </c>
+      <c r="J381" t="str">
         <f>アイテム項目!$H381</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K381">
         <f>アイテム項目!$I381</f>
@@ -22856,43 +23155,43 @@
     <row r="382" spans="1:11">
       <c r="A382" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C382,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B382" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A382,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C382" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E382,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D382" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C382,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E382">
+        <v>左底面</v>
+      </c>
+      <c r="E382" t="str">
         <f>アイテム項目!$A382</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F382" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E382,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G382">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G382" t="str">
         <f>アイテム項目!$E382</f>
-        <v>0</v>
-      </c>
-      <c r="H382">
+        <v>I-00367</v>
+      </c>
+      <c r="H382" t="str">
         <f>アイテム項目!$F382</f>
-        <v>0</v>
-      </c>
-      <c r="I382">
+        <v>丸型ミニヤスリ</v>
+      </c>
+      <c r="I382" t="str">
         <f>アイテム項目!$G382</f>
-        <v>0</v>
-      </c>
-      <c r="J382">
+        <v>工具</v>
+      </c>
+      <c r="J382" t="str">
         <f>アイテム項目!$H382</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K382">
         <f>アイテム項目!$I382</f>
@@ -22902,43 +23201,43 @@
     <row r="383" spans="1:11">
       <c r="A383" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C383,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B383" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A383,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C383" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E383,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D383" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C383,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E383">
+        <v>左底面</v>
+      </c>
+      <c r="E383" t="str">
         <f>アイテム項目!$A383</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F383" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E383,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G383">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G383" t="str">
         <f>アイテム項目!$E383</f>
-        <v>0</v>
-      </c>
-      <c r="H383">
+        <v>I-00368</v>
+      </c>
+      <c r="H383" t="str">
         <f>アイテム項目!$F383</f>
-        <v>0</v>
-      </c>
-      <c r="I383">
+        <v>ミニ切断砥石・軸付パーツ</v>
+      </c>
+      <c r="I383" t="str">
         <f>アイテム項目!$G383</f>
-        <v>0</v>
-      </c>
-      <c r="J383">
+        <v>工具</v>
+      </c>
+      <c r="J383" t="str">
         <f>アイテム項目!$H383</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K383">
         <f>アイテム項目!$I383</f>
@@ -22948,43 +23247,43 @@
     <row r="384" spans="1:11">
       <c r="A384" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C384,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B384" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A384,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C384" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E384,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D384" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C384,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E384">
+        <v>左底面</v>
+      </c>
+      <c r="E384" t="str">
         <f>アイテム項目!$A384</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F384" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E384,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G384">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G384" t="str">
         <f>アイテム項目!$E384</f>
-        <v>0</v>
-      </c>
-      <c r="H384">
+        <v>I-00369</v>
+      </c>
+      <c r="H384" t="str">
         <f>アイテム項目!$F384</f>
-        <v>0</v>
-      </c>
-      <c r="I384">
+        <v>差し替え精密ドライバー 黒</v>
+      </c>
+      <c r="I384" t="str">
         <f>アイテム項目!$G384</f>
-        <v>0</v>
-      </c>
-      <c r="J384">
+        <v>工具</v>
+      </c>
+      <c r="J384" t="str">
         <f>アイテム項目!$H384</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K384">
         <f>アイテム項目!$I384</f>
@@ -22994,43 +23293,43 @@
     <row r="385" spans="1:11">
       <c r="A385" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C385,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B385" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A385,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C385" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E385,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D385" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C385,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E385">
+        <v>左底面</v>
+      </c>
+      <c r="E385" t="str">
         <f>アイテム項目!$A385</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F385" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E385,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G385">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G385" t="str">
         <f>アイテム項目!$E385</f>
-        <v>0</v>
-      </c>
-      <c r="H385">
+        <v>I-00370</v>
+      </c>
+      <c r="H385" t="str">
         <f>アイテム項目!$F385</f>
-        <v>0</v>
-      </c>
-      <c r="I385">
+        <v>サンドペーパー各種</v>
+      </c>
+      <c r="I385" t="str">
         <f>アイテム項目!$G385</f>
-        <v>0</v>
-      </c>
-      <c r="J385">
+        <v>工具</v>
+      </c>
+      <c r="J385" t="str">
         <f>アイテム項目!$H385</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K385">
         <f>アイテム項目!$I385</f>
@@ -23040,43 +23339,43 @@
     <row r="386" spans="1:11">
       <c r="A386" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C386,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B386" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A386,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C386" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E386,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D386" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C386,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E386">
+        <v>左底面</v>
+      </c>
+      <c r="E386" t="str">
         <f>アイテム項目!$A386</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F386" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E386,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G386">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G386" t="str">
         <f>アイテム項目!$E386</f>
-        <v>0</v>
-      </c>
-      <c r="H386">
+        <v>I-00371</v>
+      </c>
+      <c r="H386" t="str">
         <f>アイテム項目!$F386</f>
-        <v>0</v>
-      </c>
-      <c r="I386">
+        <v>アルミ針金（巻）</v>
+      </c>
+      <c r="I386" t="str">
         <f>アイテム項目!$G386</f>
-        <v>0</v>
-      </c>
-      <c r="J386">
+        <v>工具</v>
+      </c>
+      <c r="J386" t="str">
         <f>アイテム項目!$H386</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K386">
         <f>アイテム項目!$I386</f>
@@ -23086,43 +23385,43 @@
     <row r="387" spans="1:11">
       <c r="A387" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C387,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B387" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A387,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C387" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E387,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D387" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C387,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E387">
+        <v>左底面</v>
+      </c>
+      <c r="E387" t="str">
         <f>アイテム項目!$A387</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F387" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E387,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G387">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G387" t="str">
         <f>アイテム項目!$E387</f>
-        <v>0</v>
-      </c>
-      <c r="H387">
+        <v>I-00372</v>
+      </c>
+      <c r="H387" t="str">
         <f>アイテム項目!$F387</f>
-        <v>0</v>
-      </c>
-      <c r="I387">
+        <v>スナップリングプライヤー 黒</v>
+      </c>
+      <c r="I387" t="str">
         <f>アイテム項目!$G387</f>
-        <v>0</v>
-      </c>
-      <c r="J387">
+        <v>工具</v>
+      </c>
+      <c r="J387" t="str">
         <f>アイテム項目!$H387</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K387">
         <f>アイテム項目!$I387</f>
@@ -23132,43 +23431,43 @@
     <row r="388" spans="1:11">
       <c r="A388" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C388,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B388" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A388,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C388" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E388,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D388" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C388,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E388">
+        <v>左底面</v>
+      </c>
+      <c r="E388" t="str">
         <f>アイテム項目!$A388</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F388" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E388,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G388">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G388" t="str">
         <f>アイテム項目!$E388</f>
-        <v>0</v>
-      </c>
-      <c r="H388">
+        <v>I-00373</v>
+      </c>
+      <c r="H388" t="str">
         <f>アイテム項目!$F388</f>
-        <v>0</v>
-      </c>
-      <c r="I388">
+        <v>六角レンチ棒各種セット（ホルダー入）</v>
+      </c>
+      <c r="I388" t="str">
         <f>アイテム項目!$G388</f>
-        <v>0</v>
-      </c>
-      <c r="J388">
+        <v>工具</v>
+      </c>
+      <c r="J388" t="str">
         <f>アイテム項目!$H388</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K388">
         <f>アイテム項目!$I388</f>
@@ -23178,43 +23477,43 @@
     <row r="389" spans="1:11">
       <c r="A389" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C389,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B389" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A389,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C389" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E389,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D389" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C389,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E389">
+        <v>左底面</v>
+      </c>
+      <c r="E389" t="str">
         <f>アイテム項目!$A389</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F389" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E389,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G389">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G389" t="str">
         <f>アイテム項目!$E389</f>
-        <v>0</v>
-      </c>
-      <c r="H389">
+        <v>I-00374</v>
+      </c>
+      <c r="H389" t="str">
         <f>アイテム項目!$F389</f>
-        <v>0</v>
-      </c>
-      <c r="I389">
+        <v>両口スパナ（大） 黒</v>
+      </c>
+      <c r="I389" t="str">
         <f>アイテム項目!$G389</f>
-        <v>0</v>
-      </c>
-      <c r="J389">
+        <v>工具</v>
+      </c>
+      <c r="J389" t="str">
         <f>アイテム項目!$H389</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K389">
         <f>アイテム項目!$I389</f>
@@ -23224,43 +23523,43 @@
     <row r="390" spans="1:11">
       <c r="A390" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C390,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B390" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A390,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C390" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E390,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D390" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C390,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E390">
+        <v>左底面</v>
+      </c>
+      <c r="E390" t="str">
         <f>アイテム項目!$A390</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F390" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E390,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G390">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G390" t="str">
         <f>アイテム項目!$E390</f>
-        <v>0</v>
-      </c>
-      <c r="H390">
+        <v>I-00375</v>
+      </c>
+      <c r="H390" t="str">
         <f>アイテム項目!$F390</f>
-        <v>0</v>
-      </c>
-      <c r="I390">
+        <v>マイナスドライバー 青白</v>
+      </c>
+      <c r="I390" t="str">
         <f>アイテム項目!$G390</f>
-        <v>0</v>
-      </c>
-      <c r="J390">
+        <v>工具</v>
+      </c>
+      <c r="J390" t="str">
         <f>アイテム項目!$H390</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K390">
         <f>アイテム項目!$I390</f>
@@ -23270,43 +23569,43 @@
     <row r="391" spans="1:11">
       <c r="A391" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C391,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B391" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A391,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C391" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E391,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D391" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C391,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E391">
+        <v>左底面</v>
+      </c>
+      <c r="E391" t="str">
         <f>アイテム項目!$A391</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F391" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E391,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G391">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G391" t="str">
         <f>アイテム項目!$E391</f>
-        <v>0</v>
-      </c>
-      <c r="H391">
+        <v>I-00376</v>
+      </c>
+      <c r="H391" t="str">
         <f>アイテム項目!$F391</f>
-        <v>0</v>
-      </c>
-      <c r="I391">
+        <v>貫通ドライバー プラス（大） 赤黒</v>
+      </c>
+      <c r="I391" t="str">
         <f>アイテム項目!$G391</f>
-        <v>0</v>
-      </c>
-      <c r="J391">
+        <v>工具</v>
+      </c>
+      <c r="J391" t="str">
         <f>アイテム項目!$H391</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K391">
         <f>アイテム項目!$I391</f>
@@ -23316,43 +23615,43 @@
     <row r="392" spans="1:11">
       <c r="A392" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C392,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B392" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A392,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C392" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E392,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D392" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C392,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E392">
+        <v>左底面</v>
+      </c>
+      <c r="E392" t="str">
         <f>アイテム項目!$A392</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F392" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E392,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G392">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G392" t="str">
         <f>アイテム項目!$E392</f>
-        <v>0</v>
-      </c>
-      <c r="H392">
+        <v>I-00377</v>
+      </c>
+      <c r="H392" t="str">
         <f>アイテム項目!$F392</f>
-        <v>0</v>
-      </c>
-      <c r="I392">
+        <v>精密ドライバー プラス 赤黒</v>
+      </c>
+      <c r="I392" t="str">
         <f>アイテム項目!$G392</f>
-        <v>0</v>
-      </c>
-      <c r="J392">
+        <v>工具</v>
+      </c>
+      <c r="J392" t="str">
         <f>アイテム項目!$H392</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K392">
         <f>アイテム項目!$I392</f>
@@ -23362,43 +23661,43 @@
     <row r="393" spans="1:11">
       <c r="A393" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C393,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B393" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A393,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C393" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E393,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D393" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C393,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E393">
+        <v>左底面</v>
+      </c>
+      <c r="E393" t="str">
         <f>アイテム項目!$A393</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F393" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E393,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G393">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G393" t="str">
         <f>アイテム項目!$E393</f>
-        <v>0</v>
-      </c>
-      <c r="H393">
+        <v>I-00378</v>
+      </c>
+      <c r="H393" t="str">
         <f>アイテム項目!$F393</f>
-        <v>0</v>
-      </c>
-      <c r="I393">
+        <v>ドライバー マイナス 赤黒</v>
+      </c>
+      <c r="I393" t="str">
         <f>アイテム項目!$G393</f>
-        <v>0</v>
-      </c>
-      <c r="J393">
+        <v>工具</v>
+      </c>
+      <c r="J393" t="str">
         <f>アイテム項目!$H393</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K393">
         <f>アイテム項目!$I393</f>
@@ -23408,43 +23707,43 @@
     <row r="394" spans="1:11">
       <c r="A394" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C394,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B394" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A394,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C394" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E394,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D394" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C394,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E394">
+        <v>左底面</v>
+      </c>
+      <c r="E394" t="str">
         <f>アイテム項目!$A394</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F394" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E394,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G394">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G394" t="str">
         <f>アイテム項目!$E394</f>
-        <v>0</v>
-      </c>
-      <c r="H394">
+        <v>I-00379</v>
+      </c>
+      <c r="H394" t="str">
         <f>アイテム項目!$F394</f>
-        <v>0</v>
-      </c>
-      <c r="I394">
+        <v>平細ヤスリ オレンジ</v>
+      </c>
+      <c r="I394" t="str">
         <f>アイテム項目!$G394</f>
-        <v>0</v>
-      </c>
-      <c r="J394">
+        <v>工具</v>
+      </c>
+      <c r="J394" t="str">
         <f>アイテム項目!$H394</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K394">
         <f>アイテム項目!$I394</f>
@@ -23454,43 +23753,43 @@
     <row r="395" spans="1:11">
       <c r="A395" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C395,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B395" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A395,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C395" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E395,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D395" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C395,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E395">
+        <v>左底面</v>
+      </c>
+      <c r="E395" t="str">
         <f>アイテム項目!$A395</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F395" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E395,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G395">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G395" t="str">
         <f>アイテム項目!$E395</f>
-        <v>0</v>
-      </c>
-      <c r="H395">
+        <v>I-00380</v>
+      </c>
+      <c r="H395" t="str">
         <f>アイテム項目!$F395</f>
-        <v>0</v>
-      </c>
-      <c r="I395">
+        <v>モンキーレンチ（中） シルバー</v>
+      </c>
+      <c r="I395" t="str">
         <f>アイテム項目!$G395</f>
-        <v>0</v>
-      </c>
-      <c r="J395">
+        <v>工具</v>
+      </c>
+      <c r="J395" t="str">
         <f>アイテム項目!$H395</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K395">
         <f>アイテム項目!$I395</f>
@@ -23500,43 +23799,43 @@
     <row r="396" spans="1:11">
       <c r="A396" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C396,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B396" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A396,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C396" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E396,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D396" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C396,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E396">
+        <v>左底面</v>
+      </c>
+      <c r="E396" t="str">
         <f>アイテム項目!$A396</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F396" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E396,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G396">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G396" t="str">
         <f>アイテム項目!$E396</f>
-        <v>0</v>
-      </c>
-      <c r="H396">
+        <v>I-00381</v>
+      </c>
+      <c r="H396" t="str">
         <f>アイテム項目!$F396</f>
-        <v>0</v>
-      </c>
-      <c r="I396">
+        <v>両口メガネレンチ（小） 5.5×7</v>
+      </c>
+      <c r="I396" t="str">
         <f>アイテム項目!$G396</f>
-        <v>0</v>
-      </c>
-      <c r="J396">
+        <v>工具</v>
+      </c>
+      <c r="J396" t="str">
         <f>アイテム項目!$H396</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K396">
         <f>アイテム項目!$I396</f>
@@ -23546,43 +23845,43 @@
     <row r="397" spans="1:11">
       <c r="A397" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C397,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B397" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A397,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C397" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E397,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D397" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C397,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E397">
+        <v>左底面</v>
+      </c>
+      <c r="E397" t="str">
         <f>アイテム項目!$A397</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F397" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E397,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G397">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G397" t="str">
         <f>アイテム項目!$E397</f>
-        <v>0</v>
-      </c>
-      <c r="H397">
+        <v>I-00382</v>
+      </c>
+      <c r="H397" t="str">
         <f>アイテム項目!$F397</f>
-        <v>0</v>
-      </c>
-      <c r="I397">
+        <v>両口メガネレンチ（中）</v>
+      </c>
+      <c r="I397" t="str">
         <f>アイテム項目!$G397</f>
-        <v>0</v>
-      </c>
-      <c r="J397">
+        <v>工具</v>
+      </c>
+      <c r="J397" t="str">
         <f>アイテム項目!$H397</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K397">
         <f>アイテム項目!$I397</f>
@@ -23592,43 +23891,43 @@
     <row r="398" spans="1:11">
       <c r="A398" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C398,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B398" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A398,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C398" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E398,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D398" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C398,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E398">
+        <v>左底面</v>
+      </c>
+      <c r="E398" t="str">
         <f>アイテム項目!$A398</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F398" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E398,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G398">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G398" t="str">
         <f>アイテム項目!$E398</f>
-        <v>0</v>
-      </c>
-      <c r="H398">
+        <v>I-00383</v>
+      </c>
+      <c r="H398" t="str">
         <f>アイテム項目!$F398</f>
-        <v>0</v>
-      </c>
-      <c r="I398">
+        <v>モーターレンチ（フックレンチ風）</v>
+      </c>
+      <c r="I398" t="str">
         <f>アイテム項目!$G398</f>
-        <v>0</v>
-      </c>
-      <c r="J398">
+        <v>工具</v>
+      </c>
+      <c r="J398" t="str">
         <f>アイテム項目!$H398</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K398">
         <f>アイテム項目!$I398</f>
@@ -23638,43 +23937,43 @@
     <row r="399" spans="1:11">
       <c r="A399" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C399,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B399" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A399,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C399" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E399,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0304</v>
       </c>
       <c r="D399" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C399,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E399">
+        <v>左底面</v>
+      </c>
+      <c r="E399" t="str">
         <f>アイテム項目!$A399</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="F399" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E399,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G399">
+        <v>パーツケース（青蓋）</v>
+      </c>
+      <c r="G399" t="str">
         <f>アイテム項目!$E399</f>
-        <v>0</v>
-      </c>
-      <c r="H399">
+        <v>I-00384</v>
+      </c>
+      <c r="H399" t="str">
         <f>アイテム項目!$F399</f>
-        <v>0</v>
-      </c>
-      <c r="I399">
+        <v>Cordless Screwdriver 電動ドライバーセット（白黒・ケース入）</v>
+      </c>
+      <c r="I399" t="str">
         <f>アイテム項目!$G399</f>
-        <v>0</v>
-      </c>
-      <c r="J399">
+        <v>工具</v>
+      </c>
+      <c r="J399" t="str">
         <f>アイテム項目!$H399</f>
-        <v>0</v>
+        <v>C-030402</v>
       </c>
       <c r="K399">
         <f>アイテム項目!$I399</f>
@@ -33290,15 +33589,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K348"/>
+  <dimension ref="A1:K399"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.75" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.25" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="7.5" style="29" customWidth="1"/>
+    <col min="6" max="6" width="44.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="29" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="29" customWidth="1"/>
@@ -41875,6 +42174,1254 @@
         <v>29</v>
       </c>
       <c r="I348"/>
+    </row>
+    <row r="351" spans="1:10">
+      <c r="A351" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B351" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C351" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D351" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E351" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F351" s="29" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G351" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H351" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="A352" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B352" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C352" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D352" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F352" s="29" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G352" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H352" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B353" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C353" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D353" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F353" s="29" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G353" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H353" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B354" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C354" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D354" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F354" s="29" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G354" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H354" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B355" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C355" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D355" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F355" s="29" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G355" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H355" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B356" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C356" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D356" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F356" s="29" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G356" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H356" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B357" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C357" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D357" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E357" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F357" s="29" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G357" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H357" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B358" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C358" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D358" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F358" s="29" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G358" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H358" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B359" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C359" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D359" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E359" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F359" s="29" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G359" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H359" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B360" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C360" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D360" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E360" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F360" s="29" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G360" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H360" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B361" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C361" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D361" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E361" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F361" s="29" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G361" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H361" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B362" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C362" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D362" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E362" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F362" s="29" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G362" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H362" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B363" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C363" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D363" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F363" s="29" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G363" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H363" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B364" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C364" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D364" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E364" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F364" s="29" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G364" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H364" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B365" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C365" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D365" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E365" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F365" s="29" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G365" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H365" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B366" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C366" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D366" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E366" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F366" s="29" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G366" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H366" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B367" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C367" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D367" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E367" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F367" s="29" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G367" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H367" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B368" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C368" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D368" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E368" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F368" s="29" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G368" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H368" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B369" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C369" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D369" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E369" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F369" s="29" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G369" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H369" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B370" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C370" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D370" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E370" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F370" s="29" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G370" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H370" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B371" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C371" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D371" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E371" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F371" s="29" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G371" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H371" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B372" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C372" s="29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D372" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E372" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F372" s="29" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G372" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H372" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B374" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C374" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D374" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E374" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F374" s="29" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G374" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H374" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B375" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C375" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D375" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E375" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F375" s="29" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G375" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H375" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B376" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C376" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D376" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E376" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F376" s="29" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G376" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H376" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B377" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C377" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D377" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E377" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F377" s="29" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G377" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H377" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B378" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C378" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D378" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E378" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F378" s="29" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G378" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H378" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B379" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C379" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D379" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E379" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F379" s="29" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G379" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H379" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B380" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C380" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D380" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E380" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F380" s="29" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G380" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H380" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B381" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C381" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D381" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E381" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F381" s="29" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G381" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H381" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B382" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C382" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D382" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E382" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F382" s="29" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G382" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H382" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B383" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C383" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D383" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E383" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F383" s="29" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G383" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H383" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B384" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C384" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D384" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E384" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F384" s="29" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G384" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H384" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B385" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C385" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D385" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E385" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F385" s="29" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G385" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H385" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B386" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C386" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D386" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E386" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F386" s="29" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G386" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H386" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B387" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C387" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D387" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E387" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F387" s="29" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G387" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H387" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B388" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C388" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D388" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E388" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F388" s="29" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G388" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H388" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B389" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C389" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D389" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E389" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F389" s="29" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G389" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H389" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B390" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C390" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D390" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E390" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F390" s="29" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G390" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H390" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B391" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C391" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D391" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E391" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F391" s="29" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G391" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H391" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B392" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C392" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D392" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E392" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F392" s="29" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G392" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H392" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B393" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C393" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D393" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E393" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F393" s="29" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G393" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H393" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B394" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C394" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D394" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E394" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F394" s="29" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G394" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H394" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B395" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C395" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D395" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E395" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F395" s="29" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G395" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H395" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B396" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C396" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D396" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E396" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F396" s="29" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G396" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H396" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B397" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C397" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D397" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E397" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F397" s="29" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G397" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H397" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B398" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C398" s="29" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D398" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E398" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F398" s="29" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G398" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H398" s="29" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B399" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C399" s="29" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D399" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E399" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F399" s="29" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G399" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H399" s="29" t="s">
+        <v>1288</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
